--- a/data/AC5.MI.xlsx
+++ b/data/AC5.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>7371</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>2.05999994277954</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>2.05999994277954</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>2.05999994277954</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AC5.MI.xlsx
+++ b/data/AC5.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>6336</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>2.05999994277954</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>2.05999994277954</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>2.05999994277954</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AC5.MI.xlsx
+++ b/data/AC5.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>5652</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>2.05999994277954</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>2.03999996185303</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>2.05999994277954</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>2.03999996185303</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AC5.MI.xlsx
+++ b/data/AC5.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>1067</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>2.07999992370605</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>2.03999996185303</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>2.07999992370605</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>2.05999994277954</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AC5.MI.xlsx
+++ b/data/AC5.MI.xlsx
@@ -62796,19 +62796,19 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>1823</v>
+        <v>5568</v>
       </c>
       <c r="C2715" t="n">
-        <v>2.09999990463257</v>
+        <v>2.14000010490417</v>
       </c>
       <c r="D2715" t="n">
         <v>2.05999994277954</v>
       </c>
       <c r="E2715" t="n">
-        <v>2.09999990463257</v>
+        <v>2.14000010490417</v>
       </c>
       <c r="F2715" t="n">
         <v>2.05999994277954</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>2142</v>
+        <v>1823</v>
       </c>
       <c r="C2716" t="n">
-        <v>2.07999992370605</v>
+        <v>2.09999990463257</v>
       </c>
       <c r="D2716" t="n">
-        <v>2.07999992370605</v>
+        <v>2.05999994277954</v>
       </c>
       <c r="E2716" t="n">
-        <v>2.07999992370605</v>
+        <v>2.09999990463257</v>
       </c>
       <c r="F2716" t="n">
-        <v>2.07999992370605</v>
+        <v>2.05999994277954</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,19 +62842,19 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>3498</v>
+        <v>2142</v>
       </c>
       <c r="C2717" t="n">
-        <v>2.14000010490417</v>
+        <v>2.07999992370605</v>
       </c>
       <c r="D2717" t="n">
         <v>2.07999992370605</v>
       </c>
       <c r="E2717" t="n">
-        <v>2.09999990463257</v>
+        <v>2.07999992370605</v>
       </c>
       <c r="F2717" t="n">
         <v>2.07999992370605</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>2112</v>
+        <v>3498</v>
       </c>
       <c r="C2718" t="n">
-        <v>2.09999990463257</v>
+        <v>2.14000010490417</v>
       </c>
       <c r="D2718" t="n">
-        <v>2.05999994277954</v>
+        <v>2.07999992370605</v>
       </c>
       <c r="E2718" t="n">
         <v>2.09999990463257</v>
       </c>
       <c r="F2718" t="n">
-        <v>2.05999994277954</v>
+        <v>2.07999992370605</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,10 +62888,10 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>7371</v>
+        <v>2112</v>
       </c>
       <c r="C2719" t="n">
         <v>2.09999990463257</v>
@@ -62900,7 +62900,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="E2719" t="n">
-        <v>2.05999994277954</v>
+        <v>2.09999990463257</v>
       </c>
       <c r="F2719" t="n">
         <v>2.05999994277954</v>
@@ -62911,10 +62911,10 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>6336</v>
+        <v>7371</v>
       </c>
       <c r="C2720" t="n">
         <v>2.09999990463257</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>5652</v>
+        <v>6336</v>
       </c>
       <c r="C2721" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="D2721" t="n">
         <v>2.05999994277954</v>
-      </c>
-      <c r="D2721" t="n">
-        <v>2.03999996185303</v>
       </c>
       <c r="E2721" t="n">
         <v>2.05999994277954</v>
       </c>
       <c r="F2721" t="n">
-        <v>2.03999996185303</v>
+        <v>2.05999994277954</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>1067</v>
+        <v>5652</v>
       </c>
       <c r="C2722" t="n">
-        <v>2.07999992370605</v>
+        <v>2.05999994277954</v>
       </c>
       <c r="D2722" t="n">
         <v>2.03999996185303</v>
       </c>
       <c r="E2722" t="n">
+        <v>2.05999994277954</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>2.03999996185303</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>875</v>
+      </c>
+      <c r="C2723" t="n">
         <v>2.07999992370605</v>
       </c>
-      <c r="F2722" t="n">
+      <c r="D2723" t="n">
         <v>2.05999994277954</v>
       </c>
-      <c r="G2722" t="s">
+      <c r="E2723" t="n">
+        <v>2.05999994277954</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>2.07999992370605</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/AC5.MI.xlsx
+++ b/data/AC5.MI.xlsx
@@ -63116,6 +63116,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2729">
+      <c r="A2729" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2729" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2729" t="n">
+        <v>2.07999992370605</v>
+      </c>
+      <c r="D2729" t="n">
+        <v>2.07999992370605</v>
+      </c>
+      <c r="E2729" t="n">
+        <v>2.07999992370605</v>
+      </c>
+      <c r="F2729" t="n">
+        <v>2.07999992370605</v>
+      </c>
+      <c r="G2729" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AC5.MI.xlsx
+++ b/data/AC5.MI.xlsx
@@ -63139,6 +63139,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2730">
+      <c r="A2730" s="1" t="n">
+        <v>46293.2916666667</v>
+      </c>
+      <c r="B2730" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2730" t="n">
+        <v>2.07999992370605</v>
+      </c>
+      <c r="D2730" t="n">
+        <v>2.07999992370605</v>
+      </c>
+      <c r="E2730" t="n">
+        <v>2.07999992370605</v>
+      </c>
+      <c r="F2730" t="n">
+        <v>2.07999992370605</v>
+      </c>
+      <c r="G2730" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AC5.MI.xlsx
+++ b/data/AC5.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>2.03999996185303</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>2.01999998092651</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>1710</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>2.03999996185303</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>2.01999998092651</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>2.03999996185303</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/AC5.MI.xlsx
+++ b/data/AC5.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>2.03999996185303</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>2.03999996185303</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>5082</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>2.01999998092651</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>2.03999996185303</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/AC5.MI.xlsx
+++ b/data/AC5.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>2.03999996185303</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>2.01999998092651</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>2596</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>2.01999998092651</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>2.01999998092651</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/AC5.MI.xlsx
+++ b/data/AC5.MI.xlsx
@@ -63339,7 +63339,9 @@
       <c r="E2738" t="n">
         <v>2.01999998092651</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>2.01999998092651</v>
+      </c>
       <c r="G2738" t="s">
         <v>7</v>
       </c>

--- a/data/AC5.MI.xlsx
+++ b/data/AC5.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>3940</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>2.07999992370605</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>2.03999996185303</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>2.05999994277954</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>2.03999996185303</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AC5.MI.xlsx
+++ b/data/AC5.MI.xlsx
@@ -427,7 +427,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G2" t="n">
-        <v>1.10515415668488</v>
+        <v>1.10515403747559</v>
       </c>
       <c r="H2" t="n">
         <v>11571</v>
@@ -456,7 +456,7 @@
         <v>1.5809999704361</v>
       </c>
       <c r="G3" t="n">
-        <v>1.08524763584137</v>
+        <v>1.08524751663208</v>
       </c>
       <c r="H3" t="n">
         <v>8559</v>
@@ -514,7 +514,7 @@
         <v>1.53799998760223</v>
       </c>
       <c r="G5" t="n">
-        <v>1.05573093891144</v>
+        <v>1.05573105812073</v>
       </c>
       <c r="H5" t="n">
         <v>35981</v>
@@ -572,7 +572,7 @@
         <v>1.53900003433228</v>
       </c>
       <c r="G7" t="n">
-        <v>1.05641734600067</v>
+        <v>1.05641746520996</v>
       </c>
       <c r="H7" t="n">
         <v>11011</v>
@@ -601,7 +601,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G8" t="n">
-        <v>1.0571037530899</v>
+        <v>1.05710387229919</v>
       </c>
       <c r="H8" t="n">
         <v>12427</v>
@@ -630,7 +630,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G9" t="n">
-        <v>1.0639683008194</v>
+        <v>1.06396818161011</v>
       </c>
       <c r="H9" t="n">
         <v>5530</v>
@@ -659,7 +659,7 @@
         <v>1.53100001811981</v>
       </c>
       <c r="G10" t="n">
-        <v>1.05092597007751</v>
+        <v>1.0509260892868</v>
       </c>
       <c r="H10" t="n">
         <v>17371</v>
@@ -688,7 +688,7 @@
         <v>1.52199995517731</v>
       </c>
       <c r="G11" t="n">
-        <v>1.04474806785583</v>
+        <v>1.04474794864655</v>
       </c>
       <c r="H11" t="n">
         <v>30875</v>
@@ -775,7 +775,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G14" t="n">
-        <v>0.892360329627991</v>
+        <v>0.892360270023346</v>
       </c>
       <c r="H14" t="n">
         <v>40364</v>
@@ -804,7 +804,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G15" t="n">
-        <v>0.957571446895599</v>
+        <v>0.95757132768631</v>
       </c>
       <c r="H15" t="n">
         <v>32601</v>
@@ -833,7 +833,7 @@
         <v>1.45899999141693</v>
       </c>
       <c r="G16" t="n">
-        <v>1.00150299072266</v>
+        <v>1.00150287151337</v>
       </c>
       <c r="H16" t="n">
         <v>14753</v>
@@ -891,7 +891,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G18" t="n">
-        <v>0.981596350669861</v>
+        <v>0.98159658908844</v>
       </c>
       <c r="H18" t="n">
         <v>17286</v>
@@ -920,7 +920,7 @@
         <v>1.48099994659424</v>
       </c>
       <c r="G19" t="n">
-        <v>1.01660442352295</v>
+        <v>1.01660454273224</v>
       </c>
       <c r="H19" t="n">
         <v>13885</v>
@@ -949,7 +949,7 @@
         <v>1.44900000095367</v>
       </c>
       <c r="G20" t="n">
-        <v>0.994638621807098</v>
+        <v>0.994638741016388</v>
       </c>
       <c r="H20" t="n">
         <v>12171</v>
@@ -978,7 +978,7 @@
         <v>1.4559999704361</v>
       </c>
       <c r="G21" t="n">
-        <v>0.999443590641022</v>
+        <v>0.999443650245667</v>
       </c>
       <c r="H21" t="n">
         <v>26252</v>
@@ -1036,7 +1036,7 @@
         <v>1.46700000762939</v>
       </c>
       <c r="G23" t="n">
-        <v>1.0069944858551</v>
+        <v>1.00699424743652</v>
       </c>
       <c r="H23" t="n">
         <v>16338</v>
@@ -1065,7 +1065,7 @@
         <v>1.44099998474121</v>
       </c>
       <c r="G24" t="n">
-        <v>0.989147126674652</v>
+        <v>0.989147245883942</v>
       </c>
       <c r="H24" t="n">
         <v>24183</v>
@@ -1094,7 +1094,7 @@
         <v>1.43299996852875</v>
       </c>
       <c r="G25" t="n">
-        <v>0.983655691146851</v>
+        <v>0.983655571937561</v>
       </c>
       <c r="H25" t="n">
         <v>32020</v>
@@ -1181,7 +1181,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G28" t="n">
-        <v>0.882750391960144</v>
+        <v>0.882750451564789</v>
       </c>
       <c r="H28" t="n">
         <v>40414</v>
@@ -1239,7 +1239,7 @@
         <v>1.31900000572205</v>
       </c>
       <c r="G30" t="n">
-        <v>0.905402541160583</v>
+        <v>0.905402660369873</v>
       </c>
       <c r="H30" t="n">
         <v>21169</v>
@@ -1268,7 +1268,7 @@
         <v>1.38399994373322</v>
       </c>
       <c r="G31" t="n">
-        <v>0.950020551681519</v>
+        <v>0.950020670890808</v>
       </c>
       <c r="H31" t="n">
         <v>22980</v>
@@ -1297,7 +1297,7 @@
         <v>1.36199998855591</v>
       </c>
       <c r="G32" t="n">
-        <v>0.934919238090515</v>
+        <v>0.934918999671936</v>
       </c>
       <c r="H32" t="n">
         <v>14081</v>
@@ -1355,7 +1355,7 @@
         <v>1.35099995136261</v>
       </c>
       <c r="G34" t="n">
-        <v>0.9273681640625</v>
+        <v>0.927368402481079</v>
       </c>
       <c r="H34" t="n">
         <v>49561</v>
@@ -1384,7 +1384,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G35" t="n">
-        <v>0.981596350669861</v>
+        <v>0.98159658908844</v>
       </c>
       <c r="H35" t="n">
         <v>21203</v>
@@ -1413,7 +1413,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G36" t="n">
-        <v>0.967867732048035</v>
+        <v>0.967867851257324</v>
       </c>
       <c r="H36" t="n">
         <v>16489</v>
@@ -1442,7 +1442,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G37" t="n">
-        <v>0.981596350669861</v>
+        <v>0.98159658908844</v>
       </c>
       <c r="H37" t="n">
         <v>11251</v>
@@ -1500,7 +1500,7 @@
         <v>1.38900005817413</v>
       </c>
       <c r="G39" t="n">
-        <v>0.95345276594162</v>
+        <v>0.953452825546265</v>
       </c>
       <c r="H39" t="n">
         <v>2781</v>
@@ -1529,7 +1529,7 @@
         <v>1.39199995994568</v>
       </c>
       <c r="G40" t="n">
-        <v>0.955512166023254</v>
+        <v>0.955512046813965</v>
       </c>
       <c r="H40" t="n">
         <v>15778</v>
@@ -1558,7 +1558,7 @@
         <v>1.375</v>
       </c>
       <c r="G41" t="n">
-        <v>0.943842589855194</v>
+        <v>0.943842470645905</v>
       </c>
       <c r="H41" t="n">
         <v>7413</v>
@@ -1587,7 +1587,7 @@
         <v>1.39100003242493</v>
       </c>
       <c r="G42" t="n">
-        <v>0.954825580120087</v>
+        <v>0.954825699329376</v>
       </c>
       <c r="H42" t="n">
         <v>5254</v>
@@ -1645,7 +1645,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G44" t="n">
-        <v>0.981596350669861</v>
+        <v>0.98159658908844</v>
       </c>
       <c r="H44" t="n">
         <v>2888</v>
@@ -1703,7 +1703,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G46" t="n">
-        <v>0.961003482341766</v>
+        <v>0.961003363132477</v>
       </c>
       <c r="H46" t="n">
         <v>16156</v>
@@ -1790,7 +1790,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G49" t="n">
-        <v>0.978164196014404</v>
+        <v>0.978164076805115</v>
       </c>
       <c r="H49" t="n">
         <v>18358</v>
@@ -1819,7 +1819,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G50" t="n">
-        <v>0.967867732048035</v>
+        <v>0.967867851257324</v>
       </c>
       <c r="H50" t="n">
         <v>29879</v>
@@ -1848,7 +1848,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G51" t="n">
-        <v>0.964435696601868</v>
+        <v>0.964435577392578</v>
       </c>
       <c r="H51" t="n">
         <v>35274</v>
@@ -1877,7 +1877,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G52" t="n">
-        <v>0.961003482341766</v>
+        <v>0.961003363132477</v>
       </c>
       <c r="H52" t="n">
         <v>4372</v>
@@ -1906,7 +1906,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G53" t="n">
-        <v>0.985028684139252</v>
+        <v>0.985028564929962</v>
       </c>
       <c r="H53" t="n">
         <v>35799</v>
@@ -1993,7 +1993,7 @@
         <v>1.41299998760223</v>
       </c>
       <c r="G56" t="n">
-        <v>0.969926953315735</v>
+        <v>0.969927072525024</v>
       </c>
       <c r="H56" t="n">
         <v>3817</v>
@@ -2051,7 +2051,7 @@
         <v>1.40699994564056</v>
       </c>
       <c r="G58" t="n">
-        <v>0.965808391571045</v>
+        <v>0.965808510780334</v>
       </c>
       <c r="H58" t="n">
         <v>10783</v>
@@ -2080,7 +2080,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G59" t="n">
-        <v>0.967867732048035</v>
+        <v>0.967867851257324</v>
       </c>
       <c r="H59" t="n">
         <v>3913</v>
@@ -2109,7 +2109,7 @@
         <v>1.38199996948242</v>
       </c>
       <c r="G60" t="n">
-        <v>0.948647797107697</v>
+        <v>0.948647677898407</v>
       </c>
       <c r="H60" t="n">
         <v>9985</v>
@@ -2138,7 +2138,7 @@
         <v>1.38399994373322</v>
       </c>
       <c r="G61" t="n">
-        <v>0.950020551681519</v>
+        <v>0.950020670890808</v>
       </c>
       <c r="H61" t="n">
         <v>31331</v>
@@ -2225,7 +2225,7 @@
         <v>1.43099999427795</v>
       </c>
       <c r="G64" t="n">
-        <v>0.982282876968384</v>
+        <v>0.982282996177673</v>
       </c>
       <c r="H64" t="n">
         <v>25067</v>
@@ -2283,7 +2283,7 @@
         <v>1.44900000095367</v>
       </c>
       <c r="G66" t="n">
-        <v>0.994638621807098</v>
+        <v>0.994638741016388</v>
       </c>
       <c r="H66" t="n">
         <v>58967</v>
@@ -2312,7 +2312,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G67" t="n">
-        <v>1.00218939781189</v>
+        <v>1.0021892786026</v>
       </c>
       <c r="H67" t="n">
         <v>30021</v>
@@ -2341,7 +2341,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G68" t="n">
-        <v>1.05984961986542</v>
+        <v>1.05984973907471</v>
       </c>
       <c r="H68" t="n">
         <v>63731</v>
@@ -2399,7 +2399,7 @@
         <v>1.52300000190735</v>
       </c>
       <c r="G70" t="n">
-        <v>1.04543471336365</v>
+        <v>1.04543447494507</v>
       </c>
       <c r="H70" t="n">
         <v>18574</v>
@@ -2515,7 +2515,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G74" t="n">
-        <v>1.12574696540833</v>
+        <v>1.12574708461761</v>
       </c>
       <c r="H74" t="n">
         <v>23139</v>
@@ -2544,7 +2544,7 @@
         <v>1.58899998664856</v>
       </c>
       <c r="G75" t="n">
-        <v>1.09073901176453</v>
+        <v>1.09073877334595</v>
       </c>
       <c r="H75" t="n">
         <v>41824</v>
@@ -2602,7 +2602,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G77" t="n">
-        <v>1.11201858520508</v>
+        <v>1.1120183467865</v>
       </c>
       <c r="H77" t="n">
         <v>282698</v>
@@ -2631,7 +2631,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G78" t="n">
-        <v>1.12574696540833</v>
+        <v>1.12574708461761</v>
       </c>
       <c r="H78" t="n">
         <v>74957</v>
@@ -2660,7 +2660,7 @@
         <v>1.567999958992</v>
       </c>
       <c r="G79" t="n">
-        <v>1.07632398605347</v>
+        <v>1.07632386684418</v>
       </c>
       <c r="H79" t="n">
         <v>142553</v>
@@ -2689,7 +2689,7 @@
         <v>1.54100000858307</v>
       </c>
       <c r="G80" t="n">
-        <v>1.05779027938843</v>
+        <v>1.05779051780701</v>
       </c>
       <c r="H80" t="n">
         <v>11036</v>
@@ -2776,7 +2776,7 @@
         <v>1.61099994182587</v>
       </c>
       <c r="G83" t="n">
-        <v>1.10584044456482</v>
+        <v>1.10584056377411</v>
       </c>
       <c r="H83" t="n">
         <v>75304</v>
@@ -2863,7 +2863,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G86" t="n">
-        <v>1.09485769271851</v>
+        <v>1.09485745429993</v>
       </c>
       <c r="H86" t="n">
         <v>10564</v>
@@ -2892,7 +2892,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G87" t="n">
-        <v>1.08799338340759</v>
+        <v>1.08799314498901</v>
       </c>
       <c r="H87" t="n">
         <v>8587</v>
@@ -2921,7 +2921,7 @@
         <v>1.60699999332428</v>
       </c>
       <c r="G88" t="n">
-        <v>1.10309493541718</v>
+        <v>1.10309481620789</v>
       </c>
       <c r="H88" t="n">
         <v>27204</v>
@@ -2950,7 +2950,7 @@
         <v>1.64699995517731</v>
       </c>
       <c r="G89" t="n">
-        <v>1.13055193424225</v>
+        <v>1.13055181503296</v>
       </c>
       <c r="H89" t="n">
         <v>32638</v>
@@ -2979,7 +2979,7 @@
         <v>1.64300000667572</v>
       </c>
       <c r="G90" t="n">
-        <v>1.12780630588531</v>
+        <v>1.1278064250946</v>
       </c>
       <c r="H90" t="n">
         <v>49552</v>
@@ -3037,7 +3037,7 @@
         <v>1.68099999427795</v>
       </c>
       <c r="G92" t="n">
-        <v>1.1538907289505</v>
+        <v>1.15389060974121</v>
       </c>
       <c r="H92" t="n">
         <v>62422</v>
@@ -3095,7 +3095,7 @@
         <v>1.70099997520447</v>
       </c>
       <c r="G94" t="n">
-        <v>1.16761934757233</v>
+        <v>1.16761946678162</v>
       </c>
       <c r="H94" t="n">
         <v>63417</v>
@@ -3124,7 +3124,7 @@
         <v>1.692999958992</v>
       </c>
       <c r="G95" t="n">
-        <v>1.16212773323059</v>
+        <v>1.16212785243988</v>
       </c>
       <c r="H95" t="n">
         <v>18409</v>
@@ -3153,7 +3153,7 @@
         <v>1.71700000762939</v>
       </c>
       <c r="G96" t="n">
-        <v>1.17860209941864</v>
+        <v>1.17860221862793</v>
       </c>
       <c r="H96" t="n">
         <v>50037</v>
@@ -3182,7 +3182,7 @@
         <v>1.71399998664856</v>
       </c>
       <c r="G97" t="n">
-        <v>1.17654275894165</v>
+        <v>1.17654287815094</v>
       </c>
       <c r="H97" t="n">
         <v>2311</v>
@@ -3269,7 +3269,7 @@
         <v>1.68799996376038</v>
       </c>
       <c r="G100" t="n">
-        <v>1.19060575962067</v>
+        <v>1.19060587882996</v>
       </c>
       <c r="H100" t="n">
         <v>14109</v>
@@ -3298,7 +3298,7 @@
         <v>1.68799996376038</v>
       </c>
       <c r="G101" t="n">
-        <v>1.19060575962067</v>
+        <v>1.19060587882996</v>
       </c>
       <c r="H101" t="n">
         <v>13817</v>
@@ -3385,7 +3385,7 @@
         <v>1.62300002574921</v>
       </c>
       <c r="G104" t="n">
-        <v>1.14475917816162</v>
+        <v>1.14475905895233</v>
       </c>
       <c r="H104" t="n">
         <v>15669</v>
@@ -3414,7 +3414,7 @@
         <v>1.58899998664856</v>
       </c>
       <c r="G105" t="n">
-        <v>1.1207777261734</v>
+        <v>1.12077760696411</v>
       </c>
       <c r="H105" t="n">
         <v>40535</v>
@@ -3443,7 +3443,7 @@
         <v>1.59300005435944</v>
       </c>
       <c r="G106" t="n">
-        <v>1.12359893321991</v>
+        <v>1.1235990524292</v>
       </c>
       <c r="H106" t="n">
         <v>17597</v>
@@ -3472,7 +3472,7 @@
         <v>1.58800005912781</v>
       </c>
       <c r="G107" t="n">
-        <v>1.12007236480713</v>
+        <v>1.12007224559784</v>
       </c>
       <c r="H107" t="n">
         <v>6906</v>
@@ -3501,7 +3501,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G108" t="n">
-        <v>1.12148284912109</v>
+        <v>1.12148296833038</v>
       </c>
       <c r="H108" t="n">
         <v>3245</v>
@@ -3530,7 +3530,7 @@
         <v>1.58899998664856</v>
       </c>
       <c r="G109" t="n">
-        <v>1.1207777261734</v>
+        <v>1.12077760696411</v>
       </c>
       <c r="H109" t="n">
         <v>14376</v>
@@ -3559,7 +3559,7 @@
         <v>1.58800005912781</v>
       </c>
       <c r="G110" t="n">
-        <v>1.12007236480713</v>
+        <v>1.12007224559784</v>
       </c>
       <c r="H110" t="n">
         <v>18181</v>
@@ -3646,7 +3646,7 @@
         <v>1.57700002193451</v>
       </c>
       <c r="G113" t="n">
-        <v>1.11231350898743</v>
+        <v>1.11231374740601</v>
       </c>
       <c r="H113" t="n">
         <v>17783</v>
@@ -3675,7 +3675,7 @@
         <v>1.55900001525879</v>
       </c>
       <c r="G114" t="n">
-        <v>1.09961771965027</v>
+        <v>1.09961760044098</v>
       </c>
       <c r="H114" t="n">
         <v>7114</v>
@@ -3704,7 +3704,7 @@
         <v>1.52799999713898</v>
       </c>
       <c r="G115" t="n">
-        <v>1.07775211334229</v>
+        <v>1.07775223255157</v>
       </c>
       <c r="H115" t="n">
         <v>25179</v>
@@ -3733,7 +3733,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G116" t="n">
-        <v>1.06152951717377</v>
+        <v>1.06152939796448</v>
       </c>
       <c r="H116" t="n">
         <v>39821</v>
@@ -3762,7 +3762,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G117" t="n">
-        <v>1.06505620479584</v>
+        <v>1.06505608558655</v>
       </c>
       <c r="H117" t="n">
         <v>21193</v>
@@ -3820,7 +3820,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G119" t="n">
-        <v>1.10384941101074</v>
+        <v>1.10384953022003</v>
       </c>
       <c r="H119" t="n">
         <v>18201</v>
@@ -3849,7 +3849,7 @@
         <v>1.54299998283386</v>
       </c>
       <c r="G120" t="n">
-        <v>1.08833229541779</v>
+        <v>1.08833241462708</v>
       </c>
       <c r="H120" t="n">
         <v>17819</v>
@@ -3878,7 +3878,7 @@
         <v>1.53299999237061</v>
       </c>
       <c r="G121" t="n">
-        <v>1.08127892017365</v>
+        <v>1.08127880096436</v>
       </c>
       <c r="H121" t="n">
         <v>21318</v>
@@ -3936,7 +3936,7 @@
         <v>1.54299998283386</v>
       </c>
       <c r="G123" t="n">
-        <v>1.08833229541779</v>
+        <v>1.08833241462708</v>
       </c>
       <c r="H123" t="n">
         <v>22969</v>
@@ -4023,7 +4023,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G126" t="n">
-        <v>1.08974301815033</v>
+        <v>1.08974289894104</v>
       </c>
       <c r="H126" t="n">
         <v>43122</v>
@@ -4081,7 +4081,7 @@
         <v>1.5809999704361</v>
       </c>
       <c r="G128" t="n">
-        <v>1.1151350736618</v>
+        <v>1.11513519287109</v>
       </c>
       <c r="H128" t="n">
         <v>29293</v>
@@ -4139,7 +4139,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G130" t="n">
-        <v>1.13911640644073</v>
+        <v>1.13911628723145</v>
       </c>
       <c r="H130" t="n">
         <v>33159</v>
@@ -4197,7 +4197,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G132" t="n">
-        <v>1.13558983802795</v>
+        <v>1.13558971881866</v>
       </c>
       <c r="H132" t="n">
         <v>7640</v>
@@ -4255,7 +4255,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G134" t="n">
-        <v>1.13911640644073</v>
+        <v>1.13911628723145</v>
       </c>
       <c r="H134" t="n">
         <v>10558</v>
@@ -4284,7 +4284,7 @@
         <v>1.61699998378754</v>
       </c>
       <c r="G135" t="n">
-        <v>1.1405268907547</v>
+        <v>1.14052712917328</v>
       </c>
       <c r="H135" t="n">
         <v>9615</v>
@@ -4313,7 +4313,7 @@
         <v>1.64600002765656</v>
       </c>
       <c r="G136" t="n">
-        <v>1.16098201274872</v>
+        <v>1.16098189353943</v>
       </c>
       <c r="H136" t="n">
         <v>24784</v>
@@ -4342,7 +4342,7 @@
         <v>1.60500001907349</v>
       </c>
       <c r="G137" t="n">
-        <v>1.13206303119659</v>
+        <v>1.1320629119873</v>
       </c>
       <c r="H137" t="n">
         <v>19943</v>
@@ -4458,7 +4458,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G141" t="n">
-        <v>1.14264321327209</v>
+        <v>1.14264309406281</v>
       </c>
       <c r="H141" t="n">
         <v>8529</v>
@@ -4487,7 +4487,7 @@
         <v>1.60599994659424</v>
       </c>
       <c r="G142" t="n">
-        <v>1.13276839256287</v>
+        <v>1.13276851177216</v>
       </c>
       <c r="H142" t="n">
         <v>15595</v>
@@ -4516,7 +4516,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G143" t="n">
-        <v>1.14969635009766</v>
+        <v>1.14969646930695</v>
       </c>
       <c r="H143" t="n">
         <v>4282</v>
@@ -4545,7 +4545,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G144" t="n">
-        <v>1.14969635009766</v>
+        <v>1.14969646930695</v>
       </c>
       <c r="H144" t="n">
         <v>1246</v>
@@ -4574,7 +4574,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G145" t="n">
-        <v>1.14969635009766</v>
+        <v>1.14969646930695</v>
       </c>
       <c r="H145" t="n">
         <v>7239</v>
@@ -4603,7 +4603,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G146" t="n">
-        <v>1.14264321327209</v>
+        <v>1.14264309406281</v>
       </c>
       <c r="H146" t="n">
         <v>10386</v>
@@ -4661,7 +4661,7 @@
         <v>1.63800001144409</v>
       </c>
       <c r="G148" t="n">
-        <v>1.15533912181854</v>
+        <v>1.15533924102783</v>
       </c>
       <c r="H148" t="n">
         <v>5831</v>
@@ -4748,7 +4748,7 @@
         <v>1.65900003910065</v>
       </c>
       <c r="G151" t="n">
-        <v>1.1701512336731</v>
+        <v>1.17015111446381</v>
       </c>
       <c r="H151" t="n">
         <v>50415</v>
@@ -4777,7 +4777,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G152" t="n">
-        <v>1.17790973186493</v>
+        <v>1.17790985107422</v>
       </c>
       <c r="H152" t="n">
         <v>34089</v>
@@ -4806,7 +4806,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G153" t="n">
-        <v>1.17790973186493</v>
+        <v>1.17790985107422</v>
       </c>
       <c r="H153" t="n">
         <v>21252</v>
@@ -4835,7 +4835,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G154" t="n">
-        <v>1.17790973186493</v>
+        <v>1.17790985107422</v>
       </c>
       <c r="H154" t="n">
         <v>7556</v>
@@ -4922,7 +4922,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G157" t="n">
-        <v>1.18849003314972</v>
+        <v>1.18848979473114</v>
       </c>
       <c r="H157" t="n">
         <v>10339</v>
@@ -4951,7 +4951,7 @@
         <v>1.67299997806549</v>
       </c>
       <c r="G158" t="n">
-        <v>1.18002593517303</v>
+        <v>1.18002581596375</v>
       </c>
       <c r="H158" t="n">
         <v>46524</v>
@@ -5125,7 +5125,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G164" t="n">
-        <v>1.24844336509705</v>
+        <v>1.24844324588776</v>
       </c>
       <c r="H164" t="n">
         <v>8620</v>
@@ -5183,7 +5183,7 @@
         <v>1.74699997901917</v>
       </c>
       <c r="G166" t="n">
-        <v>1.23222076892853</v>
+        <v>1.23222064971924</v>
       </c>
       <c r="H166" t="n">
         <v>11417</v>
@@ -5241,7 +5241,7 @@
         <v>1.74699997901917</v>
       </c>
       <c r="G168" t="n">
-        <v>1.23222076892853</v>
+        <v>1.23222064971924</v>
       </c>
       <c r="H168" t="n">
         <v>13489</v>
@@ -5328,7 +5328,7 @@
         <v>1.72099995613098</v>
       </c>
       <c r="G171" t="n">
-        <v>1.21388185024261</v>
+        <v>1.21388173103333</v>
       </c>
       <c r="H171" t="n">
         <v>1473</v>
@@ -5357,7 +5357,7 @@
         <v>1.72399997711182</v>
       </c>
       <c r="G172" t="n">
-        <v>1.21599805355072</v>
+        <v>1.21599793434143</v>
       </c>
       <c r="H172" t="n">
         <v>509</v>
@@ -5415,7 +5415,7 @@
         <v>1.73399996757507</v>
       </c>
       <c r="G174" t="n">
-        <v>1.22305130958557</v>
+        <v>1.22305107116699</v>
       </c>
       <c r="H174" t="n">
         <v>5273</v>
@@ -5560,7 +5560,7 @@
         <v>1.7039999961853</v>
       </c>
       <c r="G179" t="n">
-        <v>1.20189106464386</v>
+        <v>1.20189118385315</v>
       </c>
       <c r="H179" t="n">
         <v>5852</v>
@@ -5647,7 +5647,7 @@
         <v>1.66600000858307</v>
       </c>
       <c r="G182" t="n">
-        <v>1.17508840560913</v>
+        <v>1.17508852481842</v>
       </c>
       <c r="H182" t="n">
         <v>4189</v>
@@ -5676,7 +5676,7 @@
         <v>1.63900005817413</v>
       </c>
       <c r="G183" t="n">
-        <v>1.15604436397552</v>
+        <v>1.15604424476624</v>
       </c>
       <c r="H183" t="n">
         <v>24947</v>
@@ -5705,7 +5705,7 @@
         <v>1.63800001144409</v>
       </c>
       <c r="G184" t="n">
-        <v>1.15533912181854</v>
+        <v>1.15533924102783</v>
       </c>
       <c r="H184" t="n">
         <v>28394</v>
@@ -5734,7 +5734,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G185" t="n">
-        <v>1.15322291851044</v>
+        <v>1.15322303771973</v>
       </c>
       <c r="H185" t="n">
         <v>21865</v>
@@ -5763,7 +5763,7 @@
         <v>1.63100004196167</v>
       </c>
       <c r="G186" t="n">
-        <v>1.15040171146393</v>
+        <v>1.1504020690918</v>
       </c>
       <c r="H186" t="n">
         <v>9370</v>
@@ -5850,7 +5850,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G189" t="n">
-        <v>1.14969635009766</v>
+        <v>1.14969646930695</v>
       </c>
       <c r="H189" t="n">
         <v>9325</v>
@@ -5879,7 +5879,7 @@
         <v>1.60899996757507</v>
       </c>
       <c r="G190" t="n">
-        <v>1.13488435745239</v>
+        <v>1.1348842382431</v>
       </c>
       <c r="H190" t="n">
         <v>13449</v>
@@ -5908,7 +5908,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G191" t="n">
-        <v>1.13911640644073</v>
+        <v>1.13911628723145</v>
       </c>
       <c r="H191" t="n">
         <v>7992</v>
@@ -5966,7 +5966,7 @@
         <v>1.63900005817413</v>
       </c>
       <c r="G193" t="n">
-        <v>1.15604436397552</v>
+        <v>1.15604424476624</v>
       </c>
       <c r="H193" t="n">
         <v>12352</v>
@@ -6024,7 +6024,7 @@
         <v>1.7039999961853</v>
       </c>
       <c r="G195" t="n">
-        <v>1.20189106464386</v>
+        <v>1.20189118385315</v>
       </c>
       <c r="H195" t="n">
         <v>27098</v>
@@ -6111,7 +6111,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G198" t="n">
-        <v>1.14969635009766</v>
+        <v>1.14969646930695</v>
       </c>
       <c r="H198" t="n">
         <v>19985</v>
@@ -6198,7 +6198,7 @@
         <v>1.61300003528595</v>
       </c>
       <c r="G201" t="n">
-        <v>1.13770568370819</v>
+        <v>1.13770580291748</v>
       </c>
       <c r="H201" t="n">
         <v>3521</v>
@@ -6314,7 +6314,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G205" t="n">
-        <v>1.12148284912109</v>
+        <v>1.12148296833038</v>
       </c>
       <c r="H205" t="n">
         <v>12392</v>
@@ -6401,7 +6401,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G208" t="n">
-        <v>1.14264321327209</v>
+        <v>1.14264309406281</v>
       </c>
       <c r="H208" t="n">
         <v>11751</v>
@@ -6430,7 +6430,7 @@
         <v>1.63900005817413</v>
       </c>
       <c r="G209" t="n">
-        <v>1.15604436397552</v>
+        <v>1.15604424476624</v>
       </c>
       <c r="H209" t="n">
         <v>7452</v>
@@ -6459,7 +6459,7 @@
         <v>1.63300001621246</v>
       </c>
       <c r="G210" t="n">
-        <v>1.15181255340576</v>
+        <v>1.15181243419647</v>
       </c>
       <c r="H210" t="n">
         <v>6919</v>
@@ -6488,7 +6488,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G211" t="n">
-        <v>1.14969635009766</v>
+        <v>1.14969646930695</v>
       </c>
       <c r="H211" t="n">
         <v>10300</v>
@@ -6517,7 +6517,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G212" t="n">
-        <v>1.14969635009766</v>
+        <v>1.14969646930695</v>
       </c>
       <c r="H212" t="n">
         <v>18757</v>
@@ -6546,7 +6546,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G213" t="n">
-        <v>1.13558983802795</v>
+        <v>1.13558971881866</v>
       </c>
       <c r="H213" t="n">
         <v>117047</v>
@@ -6575,7 +6575,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G214" t="n">
-        <v>1.13911640644073</v>
+        <v>1.13911628723145</v>
       </c>
       <c r="H214" t="n">
         <v>13559</v>
@@ -6662,7 +6662,7 @@
         <v>1.60899996757507</v>
       </c>
       <c r="G217" t="n">
-        <v>1.13488435745239</v>
+        <v>1.1348842382431</v>
       </c>
       <c r="H217" t="n">
         <v>10644</v>
@@ -6691,7 +6691,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G218" t="n">
-        <v>1.14264321327209</v>
+        <v>1.14264309406281</v>
       </c>
       <c r="H218" t="n">
         <v>76955</v>
@@ -6749,7 +6749,7 @@
         <v>1.60399997234344</v>
       </c>
       <c r="G220" t="n">
-        <v>1.13135743141174</v>
+        <v>1.13135766983032</v>
       </c>
       <c r="H220" t="n">
         <v>8338</v>
@@ -6778,7 +6778,7 @@
         <v>1.60399997234344</v>
       </c>
       <c r="G221" t="n">
-        <v>1.13135743141174</v>
+        <v>1.13135766983032</v>
       </c>
       <c r="H221" t="n">
         <v>13797</v>
@@ -6807,7 +6807,7 @@
         <v>1.60899996757507</v>
       </c>
       <c r="G222" t="n">
-        <v>1.13488435745239</v>
+        <v>1.1348842382431</v>
       </c>
       <c r="H222" t="n">
         <v>3292</v>
@@ -6836,7 +6836,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G223" t="n">
-        <v>1.12853622436523</v>
+        <v>1.12853634357452</v>
       </c>
       <c r="H223" t="n">
         <v>16170</v>
@@ -6865,7 +6865,7 @@
         <v>1.59599995613098</v>
       </c>
       <c r="G224" t="n">
-        <v>1.12571489810944</v>
+        <v>1.12571501731873</v>
       </c>
       <c r="H224" t="n">
         <v>12194</v>
@@ -6894,7 +6894,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G225" t="n">
-        <v>1.12853622436523</v>
+        <v>1.12853634357452</v>
       </c>
       <c r="H225" t="n">
         <v>7240</v>
@@ -6981,7 +6981,7 @@
         <v>1.55900001525879</v>
       </c>
       <c r="G228" t="n">
-        <v>1.09961771965027</v>
+        <v>1.09961760044098</v>
       </c>
       <c r="H228" t="n">
         <v>20235</v>
@@ -7010,7 +7010,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G229" t="n">
-        <v>1.07210946083069</v>
+        <v>1.07210958003998</v>
       </c>
       <c r="H229" t="n">
         <v>29179</v>
@@ -7039,7 +7039,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G230" t="n">
-        <v>1.09326958656311</v>
+        <v>1.09326946735382</v>
       </c>
       <c r="H230" t="n">
         <v>22160</v>
@@ -7184,7 +7184,7 @@
         <v>1.5110000371933</v>
       </c>
       <c r="G235" t="n">
-        <v>1.06576156616211</v>
+        <v>1.06576180458069</v>
       </c>
       <c r="H235" t="n">
         <v>5356</v>
@@ -7213,7 +7213,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G236" t="n">
-        <v>1.06505620479584</v>
+        <v>1.06505608558655</v>
       </c>
       <c r="H236" t="n">
         <v>2881</v>
@@ -7242,7 +7242,7 @@
         <v>1.50300002098083</v>
       </c>
       <c r="G237" t="n">
-        <v>1.06011867523193</v>
+        <v>1.06011879444122</v>
       </c>
       <c r="H237" t="n">
         <v>8519</v>
@@ -7271,7 +7271,7 @@
         <v>1.53400003910065</v>
       </c>
       <c r="G238" t="n">
-        <v>1.08198416233063</v>
+        <v>1.08198428153992</v>
       </c>
       <c r="H238" t="n">
         <v>7736</v>
@@ -7329,7 +7329,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G240" t="n">
-        <v>1.07563614845276</v>
+        <v>1.07563602924347</v>
       </c>
       <c r="H240" t="n">
         <v>10784</v>
@@ -7358,7 +7358,7 @@
         <v>1.557000041008</v>
       </c>
       <c r="G241" t="n">
-        <v>1.09820711612701</v>
+        <v>1.09820699691772</v>
       </c>
       <c r="H241" t="n">
         <v>38391</v>
@@ -7387,7 +7387,7 @@
         <v>1.54100000858307</v>
       </c>
       <c r="G242" t="n">
-        <v>1.08692157268524</v>
+        <v>1.08692169189453</v>
       </c>
       <c r="H242" t="n">
         <v>3073</v>
@@ -7474,7 +7474,7 @@
         <v>1.55099999904633</v>
       </c>
       <c r="G245" t="n">
-        <v>1.09397494792938</v>
+        <v>1.09397506713867</v>
       </c>
       <c r="H245" t="n">
         <v>16835</v>
@@ -7503,7 +7503,7 @@
         <v>1.55900001525879</v>
       </c>
       <c r="G246" t="n">
-        <v>1.09961771965027</v>
+        <v>1.09961760044098</v>
       </c>
       <c r="H246" t="n">
         <v>11944</v>
@@ -7561,7 +7561,7 @@
         <v>1.56099998950958</v>
       </c>
       <c r="G248" t="n">
-        <v>1.10102832317352</v>
+        <v>1.10102844238281</v>
       </c>
       <c r="H248" t="n">
         <v>24623</v>
@@ -7590,7 +7590,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G249" t="n">
-        <v>1.09326958656311</v>
+        <v>1.09326946735382</v>
       </c>
       <c r="H249" t="n">
         <v>2599</v>
@@ -7677,7 +7677,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G252" t="n">
-        <v>1.07563614845276</v>
+        <v>1.07563602924347</v>
       </c>
       <c r="H252" t="n">
         <v>5642</v>
@@ -7764,7 +7764,7 @@
         <v>1.58899998664856</v>
       </c>
       <c r="G255" t="n">
-        <v>1.1207777261734</v>
+        <v>1.12077760696411</v>
       </c>
       <c r="H255" t="n">
         <v>8731</v>
@@ -7822,7 +7822,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G257" t="n">
-        <v>1.12853622436523</v>
+        <v>1.12853634357452</v>
       </c>
       <c r="H257" t="n">
         <v>13926</v>
@@ -7851,7 +7851,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G258" t="n">
-        <v>1.14969635009766</v>
+        <v>1.14969646930695</v>
       </c>
       <c r="H258" t="n">
         <v>13647</v>
@@ -7909,7 +7909,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G260" t="n">
-        <v>1.13558983802795</v>
+        <v>1.13558971881866</v>
       </c>
       <c r="H260" t="n">
         <v>19605</v>
@@ -7938,7 +7938,7 @@
         <v>1.6139999628067</v>
       </c>
       <c r="G261" t="n">
-        <v>1.13841104507446</v>
+        <v>1.13841092586517</v>
       </c>
       <c r="H261" t="n">
         <v>10347</v>
@@ -7996,7 +7996,7 @@
         <v>1.60500001907349</v>
       </c>
       <c r="G263" t="n">
-        <v>1.13206303119659</v>
+        <v>1.1320629119873</v>
       </c>
       <c r="H263" t="n">
         <v>17146</v>
@@ -8054,7 +8054,7 @@
         <v>1.61300003528595</v>
       </c>
       <c r="G265" t="n">
-        <v>1.13770568370819</v>
+        <v>1.13770580291748</v>
       </c>
       <c r="H265" t="n">
         <v>6217</v>
@@ -8112,7 +8112,7 @@
         <v>1.59599995613098</v>
       </c>
       <c r="G267" t="n">
-        <v>1.12571489810944</v>
+        <v>1.12571501731873</v>
       </c>
       <c r="H267" t="n">
         <v>20063</v>
@@ -8141,7 +8141,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G268" t="n">
-        <v>1.12853622436523</v>
+        <v>1.12853634357452</v>
       </c>
       <c r="H268" t="n">
         <v>51722</v>
@@ -8170,7 +8170,7 @@
         <v>1.61699998378754</v>
       </c>
       <c r="G269" t="n">
-        <v>1.1405268907547</v>
+        <v>1.14052712917328</v>
       </c>
       <c r="H269" t="n">
         <v>9780</v>
@@ -8199,7 +8199,7 @@
         <v>1.61099994182587</v>
       </c>
       <c r="G270" t="n">
-        <v>1.13629496097565</v>
+        <v>1.13629508018494</v>
       </c>
       <c r="H270" t="n">
         <v>8496</v>
@@ -8228,7 +8228,7 @@
         <v>1.6139999628067</v>
       </c>
       <c r="G271" t="n">
-        <v>1.13841104507446</v>
+        <v>1.13841092586517</v>
       </c>
       <c r="H271" t="n">
         <v>6720</v>
@@ -8257,7 +8257,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G272" t="n">
-        <v>1.13558983802795</v>
+        <v>1.13558971881866</v>
       </c>
       <c r="H272" t="n">
         <v>11451</v>
@@ -8315,7 +8315,7 @@
         <v>1.55599999427795</v>
       </c>
       <c r="G274" t="n">
-        <v>1.09750163555145</v>
+        <v>1.09750175476074</v>
       </c>
       <c r="H274" t="n">
         <v>20721</v>
@@ -8344,7 +8344,7 @@
         <v>1.58800005912781</v>
       </c>
       <c r="G275" t="n">
-        <v>1.12007236480713</v>
+        <v>1.12007224559784</v>
       </c>
       <c r="H275" t="n">
         <v>9019</v>
@@ -8402,7 +8402,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G277" t="n">
-        <v>1.09326958656311</v>
+        <v>1.09326946735382</v>
       </c>
       <c r="H277" t="n">
         <v>25183</v>
@@ -8431,7 +8431,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G278" t="n">
-        <v>1.08974301815033</v>
+        <v>1.08974289894104</v>
       </c>
       <c r="H278" t="n">
         <v>61757</v>
@@ -8460,7 +8460,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G279" t="n">
-        <v>1.08268964290619</v>
+        <v>1.08268940448761</v>
       </c>
       <c r="H279" t="n">
         <v>9817</v>
@@ -8547,7 +8547,7 @@
         <v>1.58800005912781</v>
       </c>
       <c r="G282" t="n">
-        <v>1.12007236480713</v>
+        <v>1.12007224559784</v>
       </c>
       <c r="H282" t="n">
         <v>8962</v>
@@ -8663,7 +8663,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G286" t="n">
-        <v>1.07210946083069</v>
+        <v>1.07210958003998</v>
       </c>
       <c r="H286" t="n">
         <v>10767</v>
@@ -8692,7 +8692,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G287" t="n">
-        <v>1.07563614845276</v>
+        <v>1.07563602924347</v>
       </c>
       <c r="H287" t="n">
         <v>16883</v>
@@ -8721,7 +8721,7 @@
         <v>1.52900004386902</v>
       </c>
       <c r="G288" t="n">
-        <v>1.07845759391785</v>
+        <v>1.07845747470856</v>
       </c>
       <c r="H288" t="n">
         <v>21641</v>
@@ -8779,7 +8779,7 @@
         <v>1.53900003433228</v>
       </c>
       <c r="G290" t="n">
-        <v>1.08551073074341</v>
+        <v>1.0855108499527</v>
       </c>
       <c r="H290" t="n">
         <v>36193</v>
@@ -8895,7 +8895,7 @@
         <v>1.58399999141693</v>
       </c>
       <c r="G294" t="n">
-        <v>1.11725115776062</v>
+        <v>1.11725091934204</v>
       </c>
       <c r="H294" t="n">
         <v>42266</v>
@@ -8924,7 +8924,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G295" t="n">
-        <v>1.11090302467346</v>
+        <v>1.11090290546417</v>
       </c>
       <c r="H295" t="n">
         <v>13617</v>
@@ -9011,7 +9011,7 @@
         <v>1.55599999427795</v>
       </c>
       <c r="G298" t="n">
-        <v>1.09750163555145</v>
+        <v>1.09750175476074</v>
       </c>
       <c r="H298" t="n">
         <v>4413</v>
@@ -9040,7 +9040,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G299" t="n">
-        <v>1.09326958656311</v>
+        <v>1.09326946735382</v>
       </c>
       <c r="H299" t="n">
         <v>21802</v>
@@ -9098,7 +9098,7 @@
         <v>1.5809999704361</v>
       </c>
       <c r="G301" t="n">
-        <v>1.1151350736618</v>
+        <v>1.11513519287109</v>
       </c>
       <c r="H301" t="n">
         <v>11894</v>
@@ -9127,7 +9127,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G302" t="n">
-        <v>1.12500977516174</v>
+        <v>1.12500965595245</v>
       </c>
       <c r="H302" t="n">
         <v>7665</v>
@@ -9156,7 +9156,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G303" t="n">
-        <v>1.13558983802795</v>
+        <v>1.13558971881866</v>
       </c>
       <c r="H303" t="n">
         <v>21308</v>
@@ -9243,7 +9243,7 @@
         <v>1.67200005054474</v>
       </c>
       <c r="G306" t="n">
-        <v>1.17932081222534</v>
+        <v>1.17932069301605</v>
       </c>
       <c r="H306" t="n">
         <v>22606</v>
@@ -9301,7 +9301,7 @@
         <v>1.65900003910065</v>
       </c>
       <c r="G308" t="n">
-        <v>1.1701512336731</v>
+        <v>1.17015111446381</v>
       </c>
       <c r="H308" t="n">
         <v>18060</v>
@@ -9504,7 +9504,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G315" t="n">
-        <v>1.19554328918457</v>
+        <v>1.19554316997528</v>
       </c>
       <c r="H315" t="n">
         <v>18589</v>
@@ -9533,7 +9533,7 @@
         <v>1.67200005054474</v>
       </c>
       <c r="G316" t="n">
-        <v>1.17932081222534</v>
+        <v>1.17932069301605</v>
       </c>
       <c r="H316" t="n">
         <v>30754</v>
@@ -9562,7 +9562,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G317" t="n">
-        <v>1.18849003314972</v>
+        <v>1.18848979473114</v>
       </c>
       <c r="H317" t="n">
         <v>34551</v>
@@ -9649,7 +9649,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G320" t="n">
-        <v>1.18849003314972</v>
+        <v>1.18848979473114</v>
       </c>
       <c r="H320" t="n">
         <v>53944</v>
@@ -9707,7 +9707,7 @@
         <v>1.77300000190735</v>
       </c>
       <c r="G322" t="n">
-        <v>1.25055932998657</v>
+        <v>1.25055944919586</v>
       </c>
       <c r="H322" t="n">
         <v>112928</v>
@@ -9736,7 +9736,7 @@
         <v>1.78799998760223</v>
       </c>
       <c r="G323" t="n">
-        <v>1.2611391544342</v>
+        <v>1.26113939285278</v>
       </c>
       <c r="H323" t="n">
         <v>24353</v>
@@ -9794,7 +9794,7 @@
         <v>1.76800000667572</v>
       </c>
       <c r="G325" t="n">
-        <v>1.2470326423645</v>
+        <v>1.24703252315521</v>
       </c>
       <c r="H325" t="n">
         <v>46557</v>
@@ -9852,7 +9852,7 @@
         <v>1.80900001525879</v>
       </c>
       <c r="G327" t="n">
-        <v>1.27595150470734</v>
+        <v>1.27595126628876</v>
       </c>
       <c r="H327" t="n">
         <v>21518</v>
@@ -10026,7 +10026,7 @@
         <v>1.77799999713898</v>
       </c>
       <c r="G333" t="n">
-        <v>1.25408613681793</v>
+        <v>1.25408601760864</v>
       </c>
       <c r="H333" t="n">
         <v>7174</v>
@@ -10055,7 +10055,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G334" t="n">
-        <v>1.2554966211319</v>
+        <v>1.25549674034119</v>
       </c>
       <c r="H334" t="n">
         <v>18780</v>
@@ -10113,7 +10113,7 @@
         <v>1.81200003623962</v>
       </c>
       <c r="G336" t="n">
-        <v>1.27806746959686</v>
+        <v>1.27806735038757</v>
       </c>
       <c r="H336" t="n">
         <v>16929</v>
@@ -10142,7 +10142,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G337" t="n">
-        <v>1.31192338466644</v>
+        <v>1.31192362308502</v>
       </c>
       <c r="H337" t="n">
         <v>9958</v>
@@ -10171,7 +10171,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G338" t="n">
-        <v>1.2907634973526</v>
+        <v>1.29076361656189</v>
       </c>
       <c r="H338" t="n">
         <v>35059</v>
@@ -10229,7 +10229,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G340" t="n">
-        <v>1.31192338466644</v>
+        <v>1.31192362308502</v>
       </c>
       <c r="H340" t="n">
         <v>10506</v>
@@ -10258,7 +10258,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G341" t="n">
-        <v>1.33661031723022</v>
+        <v>1.33661019802094</v>
       </c>
       <c r="H341" t="n">
         <v>60820</v>
@@ -10287,7 +10287,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G342" t="n">
-        <v>1.31897687911987</v>
+        <v>1.31897699832916</v>
       </c>
       <c r="H342" t="n">
         <v>33436</v>
@@ -10316,7 +10316,7 @@
         <v>1.89600002765656</v>
       </c>
       <c r="G343" t="n">
-        <v>1.3373156785965</v>
+        <v>1.33731579780579</v>
       </c>
       <c r="H343" t="n">
         <v>33367</v>
@@ -10345,7 +10345,7 @@
         <v>1.85800004005432</v>
       </c>
       <c r="G344" t="n">
-        <v>1.3105126619339</v>
+        <v>1.31051290035248</v>
       </c>
       <c r="H344" t="n">
         <v>51077</v>
@@ -10403,7 +10403,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G346" t="n">
-        <v>1.31192338466644</v>
+        <v>1.31192362308502</v>
       </c>
       <c r="H346" t="n">
         <v>25670</v>
@@ -10490,7 +10490,7 @@
         <v>1.90799999237061</v>
       </c>
       <c r="G349" t="n">
-        <v>1.34577965736389</v>
+        <v>1.3457795381546</v>
       </c>
       <c r="H349" t="n">
         <v>54894</v>
@@ -10577,7 +10577,7 @@
         <v>1.88800001144409</v>
       </c>
       <c r="G352" t="n">
-        <v>1.33167290687561</v>
+        <v>1.33167278766632</v>
       </c>
       <c r="H352" t="n">
         <v>21094</v>
@@ -10606,7 +10606,7 @@
         <v>1.87399995326996</v>
       </c>
       <c r="G353" t="n">
-        <v>1.32179808616638</v>
+        <v>1.32179820537567</v>
       </c>
       <c r="H353" t="n">
         <v>25431</v>
@@ -10635,7 +10635,7 @@
         <v>1.89699995517731</v>
       </c>
       <c r="G354" t="n">
-        <v>1.33802092075348</v>
+        <v>1.33802080154419</v>
       </c>
       <c r="H354" t="n">
         <v>44648</v>
@@ -10664,7 +10664,7 @@
         <v>1.88800001144409</v>
       </c>
       <c r="G355" t="n">
-        <v>1.36772263050079</v>
+        <v>1.3677225112915</v>
       </c>
       <c r="H355" t="n">
         <v>55643</v>
@@ -10751,7 +10751,7 @@
         <v>2.04399991035461</v>
       </c>
       <c r="G358" t="n">
-        <v>1.4807333946228</v>
+        <v>1.48073351383209</v>
       </c>
       <c r="H358" t="n">
         <v>89784</v>
@@ -10838,7 +10838,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G361" t="n">
-        <v>1.54738104343414</v>
+        <v>1.54738092422485</v>
       </c>
       <c r="H361" t="n">
         <v>60916</v>
@@ -11012,7 +11012,7 @@
         <v>1.96700000762939</v>
       </c>
       <c r="G367" t="n">
-        <v>1.42495250701904</v>
+        <v>1.42495262622833</v>
       </c>
       <c r="H367" t="n">
         <v>26372</v>
@@ -11128,7 +11128,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G371" t="n">
-        <v>1.39090430736542</v>
+        <v>1.39090418815613</v>
       </c>
       <c r="H371" t="n">
         <v>44565</v>
@@ -11244,7 +11244,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G375" t="n">
-        <v>1.39090430736542</v>
+        <v>1.39090418815613</v>
       </c>
       <c r="H375" t="n">
         <v>47467</v>
@@ -11273,7 +11273,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G376" t="n">
-        <v>1.38003778457642</v>
+        <v>1.38003790378571</v>
       </c>
       <c r="H376" t="n">
         <v>29249</v>
@@ -11302,7 +11302,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G377" t="n">
-        <v>1.38365995883942</v>
+        <v>1.38366007804871</v>
       </c>
       <c r="H377" t="n">
         <v>93495</v>
@@ -11331,7 +11331,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G378" t="n">
-        <v>1.35468280315399</v>
+        <v>1.35468292236328</v>
       </c>
       <c r="H378" t="n">
         <v>129917</v>
@@ -11360,7 +11360,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G379" t="n">
-        <v>1.40539288520813</v>
+        <v>1.40539300441742</v>
       </c>
       <c r="H379" t="n">
         <v>60566</v>
@@ -11505,7 +11505,7 @@
         <v>1.88699996471405</v>
       </c>
       <c r="G384" t="n">
-        <v>1.36699819564819</v>
+        <v>1.3669980764389</v>
       </c>
       <c r="H384" t="n">
         <v>11458</v>
@@ -11592,7 +11592,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G387" t="n">
-        <v>1.3691713809967</v>
+        <v>1.36917126178741</v>
       </c>
       <c r="H387" t="n">
         <v>16878</v>
@@ -11621,7 +11621,7 @@
         <v>1.89699995517731</v>
       </c>
       <c r="G388" t="n">
-        <v>1.3742424249649</v>
+        <v>1.37424230575562</v>
       </c>
       <c r="H388" t="n">
         <v>10413</v>
@@ -11650,7 +11650,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G389" t="n">
-        <v>1.3655492067337</v>
+        <v>1.36554932594299</v>
       </c>
       <c r="H389" t="n">
         <v>8799</v>
@@ -11737,7 +11737,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G392" t="n">
-        <v>1.40539288520813</v>
+        <v>1.40539300441742</v>
       </c>
       <c r="H392" t="n">
         <v>32999</v>
@@ -11766,7 +11766,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G393" t="n">
-        <v>1.42350375652313</v>
+        <v>1.42350363731384</v>
       </c>
       <c r="H393" t="n">
         <v>13143</v>
@@ -11824,7 +11824,7 @@
         <v>1.95099997520447</v>
       </c>
       <c r="G395" t="n">
-        <v>1.41336143016815</v>
+        <v>1.41336154937744</v>
       </c>
       <c r="H395" t="n">
         <v>15005</v>
@@ -11853,7 +11853,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G396" t="n">
-        <v>1.41263711452484</v>
+        <v>1.41263723373413</v>
       </c>
       <c r="H396" t="n">
         <v>5845</v>
@@ -11882,7 +11882,7 @@
         <v>1.98399996757507</v>
       </c>
       <c r="G397" t="n">
-        <v>1.43726766109467</v>
+        <v>1.43726778030396</v>
       </c>
       <c r="H397" t="n">
         <v>21666</v>
@@ -11911,7 +11911,7 @@
         <v>1.98399996757507</v>
       </c>
       <c r="G398" t="n">
-        <v>1.43726766109467</v>
+        <v>1.43726778030396</v>
       </c>
       <c r="H398" t="n">
         <v>0</v>
@@ -12143,7 +12143,7 @@
         <v>1.97099995613098</v>
       </c>
       <c r="G406" t="n">
-        <v>1.42785000801086</v>
+        <v>1.42785012722015</v>
       </c>
       <c r="H406" t="n">
         <v>32437</v>
@@ -12172,7 +12172,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G407" t="n">
-        <v>1.44161438941956</v>
+        <v>1.44161450862885</v>
       </c>
       <c r="H407" t="n">
         <v>9889</v>
@@ -12317,7 +12317,7 @@
         <v>2.00200009346008</v>
       </c>
       <c r="G412" t="n">
-        <v>1.45030748844147</v>
+        <v>1.45030760765076</v>
       </c>
       <c r="H412" t="n">
         <v>21497</v>
@@ -12346,7 +12346,7 @@
         <v>2.0239999294281</v>
       </c>
       <c r="G413" t="n">
-        <v>1.46624493598938</v>
+        <v>1.46624481678009</v>
       </c>
       <c r="H413" t="n">
         <v>19134</v>
@@ -12375,7 +12375,7 @@
         <v>1.98699998855591</v>
       </c>
       <c r="G414" t="n">
-        <v>1.43944096565247</v>
+        <v>1.43944108486176</v>
       </c>
       <c r="H414" t="n">
         <v>11595</v>
@@ -12433,7 +12433,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G416" t="n">
-        <v>1.47059142589569</v>
+        <v>1.47059154510498</v>
       </c>
       <c r="H416" t="n">
         <v>23279</v>
@@ -12549,7 +12549,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G420" t="n">
-        <v>1.49232411384583</v>
+        <v>1.49232423305511</v>
       </c>
       <c r="H420" t="n">
         <v>35761</v>
@@ -12694,7 +12694,7 @@
         <v>1.97200000286102</v>
       </c>
       <c r="G425" t="n">
-        <v>1.42857444286346</v>
+        <v>1.42857432365417</v>
       </c>
       <c r="H425" t="n">
         <v>51241</v>
@@ -12723,7 +12723,7 @@
         <v>1.9559999704361</v>
       </c>
       <c r="G426" t="n">
-        <v>1.41698372364044</v>
+        <v>1.41698360443115</v>
       </c>
       <c r="H426" t="n">
         <v>19593</v>
@@ -12810,7 +12810,7 @@
         <v>1.98699998855591</v>
       </c>
       <c r="G429" t="n">
-        <v>1.43944096565247</v>
+        <v>1.43944108486176</v>
       </c>
       <c r="H429" t="n">
         <v>4128</v>
@@ -12984,7 +12984,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G435" t="n">
-        <v>1.47638702392578</v>
+        <v>1.4763867855072</v>
       </c>
       <c r="H435" t="n">
         <v>14872</v>
@@ -13013,7 +13013,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G436" t="n">
-        <v>1.49232411384583</v>
+        <v>1.49232423305511</v>
       </c>
       <c r="H436" t="n">
         <v>10768</v>
@@ -13129,7 +13129,7 @@
         <v>2.0239999294281</v>
       </c>
       <c r="G440" t="n">
-        <v>1.46624493598938</v>
+        <v>1.46624481678009</v>
       </c>
       <c r="H440" t="n">
         <v>37007</v>
@@ -13187,7 +13187,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G442" t="n">
-        <v>1.49956870079041</v>
+        <v>1.49956858158112</v>
       </c>
       <c r="H442" t="n">
         <v>30950</v>
@@ -13216,7 +13216,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G443" t="n">
-        <v>1.49956870079041</v>
+        <v>1.49956858158112</v>
       </c>
       <c r="H443" t="n">
         <v>11593</v>
@@ -13274,7 +13274,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G445" t="n">
-        <v>1.57201170921326</v>
+        <v>1.57201159000397</v>
       </c>
       <c r="H445" t="n">
         <v>61443</v>
@@ -13390,7 +13390,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G449" t="n">
-        <v>1.64445447921753</v>
+        <v>1.64445436000824</v>
       </c>
       <c r="H449" t="n">
         <v>44146</v>
@@ -13419,7 +13419,7 @@
         <v>2.28800010681152</v>
       </c>
       <c r="G450" t="n">
-        <v>1.65749442577362</v>
+        <v>1.65749454498291</v>
       </c>
       <c r="H450" t="n">
         <v>45010</v>
@@ -13477,7 +13477,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G452" t="n">
-        <v>1.61837494373322</v>
+        <v>1.6183750629425</v>
       </c>
       <c r="H452" t="n">
         <v>35000</v>
@@ -13564,7 +13564,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G455" t="n">
-        <v>1.61692631244659</v>
+        <v>1.61692643165588</v>
       </c>
       <c r="H455" t="n">
         <v>23289</v>
@@ -13651,7 +13651,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G458" t="n">
-        <v>1.60968160629272</v>
+        <v>1.6096818447113</v>
       </c>
       <c r="H458" t="n">
         <v>18101</v>
@@ -13680,7 +13680,7 @@
         <v>2.22399997711182</v>
       </c>
       <c r="G459" t="n">
-        <v>1.61113059520721</v>
+        <v>1.61113047599792</v>
       </c>
       <c r="H459" t="n">
         <v>23889</v>
@@ -13709,7 +13709,7 @@
         <v>2.24600005149841</v>
       </c>
       <c r="G460" t="n">
-        <v>1.62706828117371</v>
+        <v>1.62706816196442</v>
       </c>
       <c r="H460" t="n">
         <v>19660</v>
@@ -13738,7 +13738,7 @@
         <v>2.24399995803833</v>
       </c>
       <c r="G461" t="n">
-        <v>1.62561917304993</v>
+        <v>1.62561905384064</v>
       </c>
       <c r="H461" t="n">
         <v>20264</v>
@@ -13796,7 +13796,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G463" t="n">
-        <v>1.57925593852997</v>
+        <v>1.57925605773926</v>
       </c>
       <c r="H463" t="n">
         <v>36257</v>
@@ -13854,7 +13854,7 @@
         <v>2.22399997711182</v>
       </c>
       <c r="G465" t="n">
-        <v>1.61113059520721</v>
+        <v>1.61113047599792</v>
       </c>
       <c r="H465" t="n">
         <v>42467</v>
@@ -13883,7 +13883,7 @@
         <v>2.22399997711182</v>
       </c>
       <c r="G466" t="n">
-        <v>1.61113059520721</v>
+        <v>1.61113047599792</v>
       </c>
       <c r="H466" t="n">
         <v>14565</v>
@@ -13912,7 +13912,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G467" t="n">
-        <v>1.60968160629272</v>
+        <v>1.6096818447113</v>
       </c>
       <c r="H467" t="n">
         <v>35706</v>
@@ -13941,7 +13941,7 @@
         <v>2.24600005149841</v>
       </c>
       <c r="G468" t="n">
-        <v>1.62706828117371</v>
+        <v>1.62706816196442</v>
       </c>
       <c r="H468" t="n">
         <v>29372</v>
@@ -14086,7 +14086,7 @@
         <v>2.3840000629425</v>
       </c>
       <c r="G473" t="n">
-        <v>1.72703945636749</v>
+        <v>1.72703957557678</v>
       </c>
       <c r="H473" t="n">
         <v>25517</v>
@@ -14115,7 +14115,7 @@
         <v>2.39400005340576</v>
       </c>
       <c r="G474" t="n">
-        <v>1.73428380489349</v>
+        <v>1.73428356647491</v>
       </c>
       <c r="H474" t="n">
         <v>59413</v>
@@ -14144,7 +14144,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G475" t="n">
-        <v>1.77485191822052</v>
+        <v>1.77485179901123</v>
       </c>
       <c r="H475" t="n">
         <v>121566</v>
@@ -14260,7 +14260,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G479" t="n">
-        <v>1.70240867137909</v>
+        <v>1.70240843296051</v>
       </c>
       <c r="H479" t="n">
         <v>51403</v>
@@ -14289,7 +14289,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G480" t="n">
-        <v>1.65025007724762</v>
+        <v>1.65024995803833</v>
       </c>
       <c r="H480" t="n">
         <v>34366</v>
@@ -14347,7 +14347,7 @@
         <v>2.34400010108948</v>
       </c>
       <c r="G482" t="n">
-        <v>1.69806241989136</v>
+        <v>1.69806206226349</v>
       </c>
       <c r="H482" t="n">
         <v>60866</v>
@@ -14376,7 +14376,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G483" t="n">
-        <v>1.711101770401</v>
+        <v>1.71110200881958</v>
       </c>
       <c r="H483" t="n">
         <v>15466</v>
@@ -14434,7 +14434,7 @@
         <v>2.40199995040894</v>
       </c>
       <c r="G485" t="n">
-        <v>1.74007892608643</v>
+        <v>1.740079164505</v>
       </c>
       <c r="H485" t="n">
         <v>12757</v>
@@ -14463,7 +14463,7 @@
         <v>2.42400002479553</v>
       </c>
       <c r="G486" t="n">
-        <v>1.75601673126221</v>
+        <v>1.75601649284363</v>
       </c>
       <c r="H486" t="n">
         <v>29903</v>
@@ -14492,7 +14492,7 @@
         <v>2.3840000629425</v>
       </c>
       <c r="G487" t="n">
-        <v>1.72703945636749</v>
+        <v>1.72703957557678</v>
       </c>
       <c r="H487" t="n">
         <v>19548</v>
@@ -14550,7 +14550,7 @@
         <v>2.31599998474121</v>
       </c>
       <c r="G489" t="n">
-        <v>1.67777836322784</v>
+        <v>1.67777824401855</v>
       </c>
       <c r="H489" t="n">
         <v>29164</v>
@@ -14608,7 +14608,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G491" t="n">
-        <v>1.68792033195496</v>
+        <v>1.68792021274567</v>
       </c>
       <c r="H491" t="n">
         <v>41375</v>
@@ -14666,7 +14666,7 @@
         <v>2.26399993896484</v>
       </c>
       <c r="G493" t="n">
-        <v>1.64010798931122</v>
+        <v>1.64010787010193</v>
       </c>
       <c r="H493" t="n">
         <v>33876</v>
@@ -14695,7 +14695,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G494" t="n">
-        <v>1.63286375999451</v>
+        <v>1.63286364078522</v>
       </c>
       <c r="H494" t="n">
         <v>32458</v>
@@ -14724,7 +14724,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G495" t="n">
-        <v>1.62272191047668</v>
+        <v>1.62272167205811</v>
       </c>
       <c r="H495" t="n">
         <v>27366</v>
@@ -14753,7 +14753,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G496" t="n">
-        <v>1.57925593852997</v>
+        <v>1.57925605773926</v>
       </c>
       <c r="H496" t="n">
         <v>63365</v>
@@ -14840,7 +14840,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G499" t="n">
-        <v>1.63286375999451</v>
+        <v>1.63286364078522</v>
       </c>
       <c r="H499" t="n">
         <v>69996</v>
@@ -14898,7 +14898,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G501" t="n">
-        <v>1.65025007724762</v>
+        <v>1.65024995803833</v>
       </c>
       <c r="H501" t="n">
         <v>29062</v>
@@ -14927,7 +14927,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G502" t="n">
-        <v>1.66184067726135</v>
+        <v>1.66184055805206</v>
       </c>
       <c r="H502" t="n">
         <v>51309</v>
@@ -14956,7 +14956,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G503" t="n">
-        <v>1.64445447921753</v>
+        <v>1.64445436000824</v>
       </c>
       <c r="H503" t="n">
         <v>18754</v>
@@ -15101,7 +15101,7 @@
         <v>2.31399989128113</v>
       </c>
       <c r="G508" t="n">
-        <v>1.67632937431335</v>
+        <v>1.67632949352264</v>
       </c>
       <c r="H508" t="n">
         <v>22153</v>
@@ -15159,7 +15159,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G510" t="n">
-        <v>1.67343175411224</v>
+        <v>1.67343151569366</v>
       </c>
       <c r="H510" t="n">
         <v>8063</v>
@@ -15275,7 +15275,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G514" t="n">
-        <v>1.67343175411224</v>
+        <v>1.67343151569366</v>
       </c>
       <c r="H514" t="n">
         <v>16235</v>
@@ -15304,7 +15304,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G515" t="n">
-        <v>1.67343175411224</v>
+        <v>1.67343151569366</v>
       </c>
       <c r="H515" t="n">
         <v>9476</v>
@@ -15333,7 +15333,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G516" t="n">
-        <v>1.67343175411224</v>
+        <v>1.67343151569366</v>
       </c>
       <c r="H516" t="n">
         <v>26334</v>
@@ -15362,7 +15362,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G517" t="n">
-        <v>1.67343175411224</v>
+        <v>1.67343151569366</v>
       </c>
       <c r="H517" t="n">
         <v>22527</v>
@@ -15391,7 +15391,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G518" t="n">
-        <v>1.67343175411224</v>
+        <v>1.67343151569366</v>
       </c>
       <c r="H518" t="n">
         <v>20045</v>
@@ -15449,7 +15449,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G520" t="n">
-        <v>1.67343175411224</v>
+        <v>1.67343151569366</v>
       </c>
       <c r="H520" t="n">
         <v>33637</v>
@@ -15478,7 +15478,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G521" t="n">
-        <v>1.71689736843109</v>
+        <v>1.71689713001251</v>
       </c>
       <c r="H521" t="n">
         <v>33424</v>
@@ -15507,7 +15507,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G522" t="n">
-        <v>1.70240867137909</v>
+        <v>1.70240843296051</v>
       </c>
       <c r="H522" t="n">
         <v>25242</v>
@@ -15536,7 +15536,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G523" t="n">
-        <v>1.68792033195496</v>
+        <v>1.68792021274567</v>
       </c>
       <c r="H523" t="n">
         <v>24997</v>
@@ -15652,7 +15652,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G527" t="n">
-        <v>1.73863053321838</v>
+        <v>1.7386302947998</v>
       </c>
       <c r="H527" t="n">
         <v>58123</v>
@@ -15768,7 +15768,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G531" t="n">
-        <v>1.81831765174866</v>
+        <v>1.81831741333008</v>
       </c>
       <c r="H531" t="n">
         <v>44587</v>
@@ -15884,7 +15884,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G535" t="n">
-        <v>1.77485191822052</v>
+        <v>1.77485179901123</v>
       </c>
       <c r="H535" t="n">
         <v>18844</v>
@@ -15942,7 +15942,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G537" t="n">
-        <v>1.71689736843109</v>
+        <v>1.71689713001251</v>
       </c>
       <c r="H537" t="n">
         <v>41037</v>
@@ -15971,7 +15971,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G538" t="n">
-        <v>1.7458747625351</v>
+        <v>1.74587464332581</v>
       </c>
       <c r="H538" t="n">
         <v>56587</v>
@@ -16087,7 +16087,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G542" t="n">
-        <v>1.71689736843109</v>
+        <v>1.71689713001251</v>
       </c>
       <c r="H542" t="n">
         <v>30534</v>
@@ -16174,7 +16174,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G545" t="n">
-        <v>1.71689736843109</v>
+        <v>1.71689713001251</v>
       </c>
       <c r="H545" t="n">
         <v>23270</v>
@@ -16203,7 +16203,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G546" t="n">
-        <v>1.73863053321838</v>
+        <v>1.7386302947998</v>
       </c>
       <c r="H546" t="n">
         <v>15401</v>
@@ -16232,7 +16232,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G547" t="n">
-        <v>1.72414195537567</v>
+        <v>1.72414171695709</v>
       </c>
       <c r="H547" t="n">
         <v>11964</v>
@@ -16348,7 +16348,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G551" t="n">
-        <v>1.72414195537567</v>
+        <v>1.72414171695709</v>
       </c>
       <c r="H551" t="n">
         <v>35134</v>
@@ -16464,7 +16464,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G555" t="n">
-        <v>1.68792033195496</v>
+        <v>1.68792021274567</v>
       </c>
       <c r="H555" t="n">
         <v>55348</v>
@@ -16551,7 +16551,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G558" t="n">
-        <v>1.68792033195496</v>
+        <v>1.68792021274567</v>
       </c>
       <c r="H558" t="n">
         <v>22189</v>
@@ -16609,7 +16609,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G560" t="n">
-        <v>1.70240867137909</v>
+        <v>1.70240843296051</v>
       </c>
       <c r="H560" t="n">
         <v>15157</v>
@@ -16638,7 +16638,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G561" t="n">
-        <v>1.71689736843109</v>
+        <v>1.71689713001251</v>
       </c>
       <c r="H561" t="n">
         <v>14014</v>
@@ -16667,7 +16667,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G562" t="n">
-        <v>1.71689736843109</v>
+        <v>1.71689713001251</v>
       </c>
       <c r="H562" t="n">
         <v>17956</v>
@@ -16725,7 +16725,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G564" t="n">
-        <v>1.71689736843109</v>
+        <v>1.71689713001251</v>
       </c>
       <c r="H564" t="n">
         <v>22966</v>
@@ -16754,7 +16754,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G565" t="n">
-        <v>1.70240867137909</v>
+        <v>1.70240843296051</v>
       </c>
       <c r="H565" t="n">
         <v>23166</v>
@@ -16783,7 +16783,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G566" t="n">
-        <v>1.68792033195496</v>
+        <v>1.68792021274567</v>
       </c>
       <c r="H566" t="n">
         <v>16494</v>
@@ -16812,7 +16812,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G567" t="n">
-        <v>1.71689736843109</v>
+        <v>1.71689713001251</v>
       </c>
       <c r="H567" t="n">
         <v>19060</v>
@@ -16841,7 +16841,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G568" t="n">
-        <v>1.71689736843109</v>
+        <v>1.71689713001251</v>
       </c>
       <c r="H568" t="n">
         <v>12715</v>
@@ -16870,7 +16870,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G569" t="n">
-        <v>1.70240867137909</v>
+        <v>1.70240843296051</v>
       </c>
       <c r="H569" t="n">
         <v>18915</v>
@@ -16928,7 +16928,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G571" t="n">
-        <v>1.67343175411224</v>
+        <v>1.67343151569366</v>
       </c>
       <c r="H571" t="n">
         <v>11034</v>
@@ -16957,7 +16957,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G572" t="n">
-        <v>1.70240867137909</v>
+        <v>1.70240843296051</v>
       </c>
       <c r="H572" t="n">
         <v>11456</v>
@@ -17044,7 +17044,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G575" t="n">
-        <v>1.67343175411224</v>
+        <v>1.67343151569366</v>
       </c>
       <c r="H575" t="n">
         <v>14610</v>
@@ -17073,7 +17073,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G576" t="n">
-        <v>1.68792033195496</v>
+        <v>1.68792021274567</v>
       </c>
       <c r="H576" t="n">
         <v>12065</v>
@@ -17189,7 +17189,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G580" t="n">
-        <v>1.70240867137909</v>
+        <v>1.70240843296051</v>
       </c>
       <c r="H580" t="n">
         <v>33193</v>
@@ -17218,7 +17218,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G581" t="n">
-        <v>1.73863053321838</v>
+        <v>1.7386302947998</v>
       </c>
       <c r="H581" t="n">
         <v>85357</v>
@@ -17247,7 +17247,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G582" t="n">
-        <v>1.70240867137909</v>
+        <v>1.70240843296051</v>
       </c>
       <c r="H582" t="n">
         <v>83292</v>
@@ -17305,7 +17305,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G584" t="n">
-        <v>1.72414195537567</v>
+        <v>1.72414171695709</v>
       </c>
       <c r="H584" t="n">
         <v>30792</v>
@@ -17334,7 +17334,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G585" t="n">
-        <v>1.73863053321838</v>
+        <v>1.7386302947998</v>
       </c>
       <c r="H585" t="n">
         <v>38165</v>
@@ -17363,7 +17363,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G586" t="n">
-        <v>1.7458747625351</v>
+        <v>1.74587464332581</v>
       </c>
       <c r="H586" t="n">
         <v>16830</v>
@@ -17392,7 +17392,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G587" t="n">
-        <v>1.73863053321838</v>
+        <v>1.7386302947998</v>
       </c>
       <c r="H587" t="n">
         <v>27164</v>
@@ -17421,7 +17421,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G588" t="n">
-        <v>1.73863053321838</v>
+        <v>1.7386302947998</v>
       </c>
       <c r="H588" t="n">
         <v>13645</v>
@@ -17450,7 +17450,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G589" t="n">
-        <v>1.73863053321838</v>
+        <v>1.7386302947998</v>
       </c>
       <c r="H589" t="n">
         <v>23580</v>
@@ -17479,7 +17479,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G590" t="n">
-        <v>1.73863053321838</v>
+        <v>1.7386302947998</v>
       </c>
       <c r="H590" t="n">
         <v>24262</v>
@@ -17537,7 +17537,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G592" t="n">
-        <v>1.73863053321838</v>
+        <v>1.7386302947998</v>
       </c>
       <c r="H592" t="n">
         <v>26024</v>
@@ -17566,7 +17566,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G593" t="n">
-        <v>1.72414195537567</v>
+        <v>1.72414171695709</v>
       </c>
       <c r="H593" t="n">
         <v>19384</v>
@@ -17595,7 +17595,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G594" t="n">
-        <v>1.71689736843109</v>
+        <v>1.71689713001251</v>
       </c>
       <c r="H594" t="n">
         <v>7113</v>
@@ -17653,7 +17653,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G596" t="n">
-        <v>1.72414195537567</v>
+        <v>1.72414171695709</v>
       </c>
       <c r="H596" t="n">
         <v>11590</v>
@@ -17682,7 +17682,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G597" t="n">
-        <v>1.73863053321838</v>
+        <v>1.7386302947998</v>
       </c>
       <c r="H597" t="n">
         <v>32398</v>
@@ -17711,7 +17711,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G598" t="n">
-        <v>1.73863053321838</v>
+        <v>1.7386302947998</v>
       </c>
       <c r="H598" t="n">
         <v>14290</v>
@@ -17740,7 +17740,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G599" t="n">
-        <v>1.71689736843109</v>
+        <v>1.71689713001251</v>
       </c>
       <c r="H599" t="n">
         <v>29493</v>
@@ -17798,7 +17798,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G601" t="n">
-        <v>1.72414195537567</v>
+        <v>1.72414171695709</v>
       </c>
       <c r="H601" t="n">
         <v>12552</v>
@@ -17856,7 +17856,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G603" t="n">
-        <v>1.73863053321838</v>
+        <v>1.7386302947998</v>
       </c>
       <c r="H603" t="n">
         <v>21816</v>
@@ -17885,7 +17885,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G604" t="n">
-        <v>1.71689736843109</v>
+        <v>1.71689713001251</v>
       </c>
       <c r="H604" t="n">
         <v>18293</v>
@@ -17943,7 +17943,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G606" t="n">
-        <v>1.78934049606323</v>
+        <v>1.78934025764465</v>
       </c>
       <c r="H606" t="n">
         <v>33656</v>
@@ -17972,7 +17972,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G607" t="n">
-        <v>1.78934049606323</v>
+        <v>1.78934025764465</v>
       </c>
       <c r="H607" t="n">
         <v>127277</v>
@@ -18001,7 +18001,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G608" t="n">
-        <v>1.78209614753723</v>
+        <v>1.78209602832794</v>
       </c>
       <c r="H608" t="n">
         <v>43846</v>
@@ -18030,7 +18030,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G609" t="n">
-        <v>1.78934049606323</v>
+        <v>1.78934025764465</v>
       </c>
       <c r="H609" t="n">
         <v>69631</v>
@@ -18059,7 +18059,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G610" t="n">
-        <v>1.78934049606323</v>
+        <v>1.78934025764465</v>
       </c>
       <c r="H610" t="n">
         <v>44275</v>
@@ -18146,7 +18146,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G613" t="n">
-        <v>1.78209614753723</v>
+        <v>1.78209602832794</v>
       </c>
       <c r="H613" t="n">
         <v>26623</v>
@@ -18175,7 +18175,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G614" t="n">
-        <v>1.78209614753723</v>
+        <v>1.78209602832794</v>
       </c>
       <c r="H614" t="n">
         <v>48061</v>
@@ -18262,7 +18262,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G617" t="n">
-        <v>1.78209614753723</v>
+        <v>1.78209602832794</v>
       </c>
       <c r="H617" t="n">
         <v>13652</v>
@@ -18291,7 +18291,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G618" t="n">
-        <v>1.77485191822052</v>
+        <v>1.77485179901123</v>
       </c>
       <c r="H618" t="n">
         <v>10841</v>
@@ -18349,7 +18349,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G620" t="n">
-        <v>1.77485191822052</v>
+        <v>1.77485179901123</v>
       </c>
       <c r="H620" t="n">
         <v>54461</v>
@@ -18378,7 +18378,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G621" t="n">
-        <v>1.78209614753723</v>
+        <v>1.78209602832794</v>
       </c>
       <c r="H621" t="n">
         <v>48684</v>
@@ -18436,7 +18436,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G623" t="n">
-        <v>1.77485191822052</v>
+        <v>1.77485179901123</v>
       </c>
       <c r="H623" t="n">
         <v>48956</v>
@@ -18465,7 +18465,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G624" t="n">
-        <v>1.77485191822052</v>
+        <v>1.77485179901123</v>
       </c>
       <c r="H624" t="n">
         <v>11758</v>
@@ -18494,7 +18494,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G625" t="n">
-        <v>1.78209614753723</v>
+        <v>1.78209602832794</v>
       </c>
       <c r="H625" t="n">
         <v>20352</v>
@@ -18523,7 +18523,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G626" t="n">
-        <v>1.78934049606323</v>
+        <v>1.78934025764465</v>
       </c>
       <c r="H626" t="n">
         <v>75320</v>
@@ -18552,7 +18552,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G627" t="n">
-        <v>1.78209614753723</v>
+        <v>1.78209602832794</v>
       </c>
       <c r="H627" t="n">
         <v>41701</v>
@@ -18581,7 +18581,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G628" t="n">
-        <v>1.78934049606323</v>
+        <v>1.78934025764465</v>
       </c>
       <c r="H628" t="n">
         <v>13142</v>
@@ -18610,7 +18610,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G629" t="n">
-        <v>1.78934049606323</v>
+        <v>1.78934025764465</v>
       </c>
       <c r="H629" t="n">
         <v>39677</v>
@@ -18639,7 +18639,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G630" t="n">
-        <v>1.81831765174866</v>
+        <v>1.81831741333008</v>
       </c>
       <c r="H630" t="n">
         <v>54770</v>
@@ -18755,7 +18755,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G634" t="n">
-        <v>1.81107330322266</v>
+        <v>1.81107318401337</v>
       </c>
       <c r="H634" t="n">
         <v>8982</v>
@@ -18784,7 +18784,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G635" t="n">
-        <v>1.82585752010345</v>
+        <v>1.82585728168488</v>
       </c>
       <c r="H635" t="n">
         <v>5272</v>
@@ -18813,7 +18813,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G636" t="n">
-        <v>1.81107330322266</v>
+        <v>1.81107318401337</v>
       </c>
       <c r="H636" t="n">
         <v>13411</v>
@@ -18842,7 +18842,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G637" t="n">
-        <v>1.81107330322266</v>
+        <v>1.81107318401337</v>
       </c>
       <c r="H637" t="n">
         <v>6690</v>
@@ -18871,7 +18871,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G638" t="n">
-        <v>1.81107330322266</v>
+        <v>1.81107318401337</v>
       </c>
       <c r="H638" t="n">
         <v>10707</v>
@@ -18987,7 +18987,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G642" t="n">
-        <v>1.81107330322266</v>
+        <v>1.81107318401337</v>
       </c>
       <c r="H642" t="n">
         <v>10904</v>
@@ -19016,7 +19016,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G643" t="n">
-        <v>1.81107330322266</v>
+        <v>1.81107318401337</v>
       </c>
       <c r="H643" t="n">
         <v>30838</v>
@@ -19074,7 +19074,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G645" t="n">
-        <v>1.81107330322266</v>
+        <v>1.81107318401337</v>
       </c>
       <c r="H645" t="n">
         <v>16522</v>
@@ -19103,7 +19103,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G646" t="n">
-        <v>1.81107330322266</v>
+        <v>1.81107318401337</v>
       </c>
       <c r="H646" t="n">
         <v>22283</v>
@@ -19132,7 +19132,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G647" t="n">
-        <v>1.81107330322266</v>
+        <v>1.81107318401337</v>
       </c>
       <c r="H647" t="n">
         <v>3602</v>
@@ -19161,7 +19161,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G648" t="n">
-        <v>1.81107330322266</v>
+        <v>1.81107318401337</v>
       </c>
       <c r="H648" t="n">
         <v>10818</v>
@@ -19190,7 +19190,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G649" t="n">
-        <v>1.81107330322266</v>
+        <v>1.81107318401337</v>
       </c>
       <c r="H649" t="n">
         <v>10374</v>
@@ -19219,7 +19219,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G650" t="n">
-        <v>1.81107330322266</v>
+        <v>1.81107318401337</v>
       </c>
       <c r="H650" t="n">
         <v>4963</v>
@@ -19248,7 +19248,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G651" t="n">
-        <v>1.81107330322266</v>
+        <v>1.81107318401337</v>
       </c>
       <c r="H651" t="n">
         <v>17501</v>
@@ -19306,7 +19306,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G653" t="n">
-        <v>1.81107330322266</v>
+        <v>1.81107318401337</v>
       </c>
       <c r="H653" t="n">
         <v>7941</v>
@@ -19335,7 +19335,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G654" t="n">
-        <v>1.81107330322266</v>
+        <v>1.81107318401337</v>
       </c>
       <c r="H654" t="n">
         <v>15713</v>
@@ -19509,7 +19509,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G660" t="n">
-        <v>1.82585752010345</v>
+        <v>1.82585728168488</v>
       </c>
       <c r="H660" t="n">
         <v>6376</v>
@@ -19538,7 +19538,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G661" t="n">
-        <v>1.82585752010345</v>
+        <v>1.82585728168488</v>
       </c>
       <c r="H661" t="n">
         <v>19372</v>
@@ -19567,7 +19567,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G662" t="n">
-        <v>1.82585752010345</v>
+        <v>1.82585728168488</v>
       </c>
       <c r="H662" t="n">
         <v>11773</v>
@@ -19625,7 +19625,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G664" t="n">
-        <v>1.82585752010345</v>
+        <v>1.82585728168488</v>
       </c>
       <c r="H664" t="n">
         <v>337641</v>
@@ -19654,7 +19654,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G665" t="n">
-        <v>1.82585752010345</v>
+        <v>1.82585728168488</v>
       </c>
       <c r="H665" t="n">
         <v>18550</v>
@@ -19770,7 +19770,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G669" t="n">
-        <v>1.82585752010345</v>
+        <v>1.82585728168488</v>
       </c>
       <c r="H669" t="n">
         <v>7550</v>
@@ -19828,7 +19828,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G671" t="n">
-        <v>1.82585752010345</v>
+        <v>1.82585728168488</v>
       </c>
       <c r="H671" t="n">
         <v>12160</v>
@@ -20031,7 +20031,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G678" t="n">
-        <v>1.82585752010345</v>
+        <v>1.82585728168488</v>
       </c>
       <c r="H678" t="n">
         <v>132998</v>
@@ -20176,7 +20176,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G683" t="n">
-        <v>1.82585752010345</v>
+        <v>1.82585728168488</v>
       </c>
       <c r="H683" t="n">
         <v>16690</v>
@@ -20205,7 +20205,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G684" t="n">
-        <v>1.82585752010345</v>
+        <v>1.82585728168488</v>
       </c>
       <c r="H684" t="n">
         <v>78883</v>
@@ -20292,7 +20292,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G687" t="n">
-        <v>1.82585752010345</v>
+        <v>1.82585728168488</v>
       </c>
       <c r="H687" t="n">
         <v>417323</v>
@@ -20524,7 +20524,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G695" t="n">
-        <v>1.75193607807159</v>
+        <v>1.75193583965302</v>
       </c>
       <c r="H695" t="n">
         <v>10449</v>
@@ -20901,7 +20901,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G708" t="n">
-        <v>1.82585752010345</v>
+        <v>1.82585728168488</v>
       </c>
       <c r="H708" t="n">
         <v>8969</v>
@@ -21133,7 +21133,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G716" t="n">
-        <v>1.73715174198151</v>
+        <v>1.73715150356293</v>
       </c>
       <c r="H716" t="n">
         <v>24640</v>
@@ -21162,7 +21162,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G717" t="n">
-        <v>1.69279909133911</v>
+        <v>1.69279885292053</v>
       </c>
       <c r="H717" t="n">
         <v>9189</v>
@@ -21365,7 +21365,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G724" t="n">
-        <v>1.6114856004715</v>
+        <v>1.61148571968079</v>
       </c>
       <c r="H724" t="n">
         <v>5427</v>
@@ -21423,7 +21423,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G726" t="n">
-        <v>1.6114856004715</v>
+        <v>1.61148571968079</v>
       </c>
       <c r="H726" t="n">
         <v>5606</v>
@@ -21452,7 +21452,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G727" t="n">
-        <v>1.59670114517212</v>
+        <v>1.59670126438141</v>
       </c>
       <c r="H727" t="n">
         <v>2000</v>
@@ -21510,7 +21510,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G729" t="n">
-        <v>1.6114856004715</v>
+        <v>1.61148571968079</v>
       </c>
       <c r="H729" t="n">
         <v>707</v>
@@ -21539,7 +21539,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G730" t="n">
-        <v>1.52277982234955</v>
+        <v>1.52277994155884</v>
       </c>
       <c r="H730" t="n">
         <v>12952</v>
@@ -21568,7 +21568,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G731" t="n">
-        <v>1.60409355163574</v>
+        <v>1.60409343242645</v>
       </c>
       <c r="H731" t="n">
         <v>3989</v>
@@ -21800,7 +21800,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G739" t="n">
-        <v>1.45994675159454</v>
+        <v>1.45994687080383</v>
       </c>
       <c r="H739" t="n">
         <v>30472</v>
@@ -21974,7 +21974,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G745" t="n">
-        <v>1.43407440185547</v>
+        <v>1.43407452106476</v>
       </c>
       <c r="H745" t="n">
         <v>3345</v>
@@ -22003,7 +22003,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G746" t="n">
-        <v>1.36384904384613</v>
+        <v>1.36384892463684</v>
       </c>
       <c r="H746" t="n">
         <v>866</v>
@@ -22206,7 +22206,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G753" t="n">
-        <v>1.31949627399445</v>
+        <v>1.31949615478516</v>
       </c>
       <c r="H753" t="n">
         <v>19716</v>
@@ -22322,7 +22322,7 @@
         <v>1.75</v>
       </c>
       <c r="G757" t="n">
-        <v>1.29362368583679</v>
+        <v>1.29362380504608</v>
       </c>
       <c r="H757" t="n">
         <v>6000</v>
@@ -22351,7 +22351,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G758" t="n">
-        <v>1.25666296482086</v>
+        <v>1.25666308403015</v>
       </c>
       <c r="H758" t="n">
         <v>24574</v>
@@ -22380,7 +22380,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G759" t="n">
-        <v>1.25666296482086</v>
+        <v>1.25666308403015</v>
       </c>
       <c r="H759" t="n">
         <v>1114</v>
@@ -22409,7 +22409,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G760" t="n">
-        <v>1.25666296482086</v>
+        <v>1.25666308403015</v>
       </c>
       <c r="H760" t="n">
         <v>8828</v>
@@ -22438,7 +22438,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G761" t="n">
-        <v>1.25666296482086</v>
+        <v>1.25666308403015</v>
       </c>
       <c r="H761" t="n">
         <v>2365</v>
@@ -22467,7 +22467,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G762" t="n">
-        <v>1.23448657989502</v>
+        <v>1.23448669910431</v>
       </c>
       <c r="H762" t="n">
         <v>11649</v>
@@ -22496,7 +22496,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G763" t="n">
-        <v>1.22339844703674</v>
+        <v>1.22339832782745</v>
       </c>
       <c r="H763" t="n">
         <v>24792</v>
@@ -22583,7 +22583,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G766" t="n">
-        <v>1.25666296482086</v>
+        <v>1.25666308403015</v>
       </c>
       <c r="H766" t="n">
         <v>100500</v>
@@ -22641,7 +22641,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G768" t="n">
-        <v>1.24927079677582</v>
+        <v>1.24927091598511</v>
       </c>
       <c r="H768" t="n">
         <v>18661</v>
@@ -22670,7 +22670,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G769" t="n">
-        <v>1.24927079677582</v>
+        <v>1.24927091598511</v>
       </c>
       <c r="H769" t="n">
         <v>1149</v>
@@ -22728,7 +22728,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G771" t="n">
-        <v>1.25666296482086</v>
+        <v>1.25666308403015</v>
       </c>
       <c r="H771" t="n">
         <v>8805</v>
@@ -22786,7 +22786,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G773" t="n">
-        <v>1.25666296482086</v>
+        <v>1.25666308403015</v>
       </c>
       <c r="H773" t="n">
         <v>5250</v>
@@ -22815,7 +22815,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G774" t="n">
-        <v>1.22339844703674</v>
+        <v>1.22339832782745</v>
       </c>
       <c r="H774" t="n">
         <v>4000</v>
@@ -22844,7 +22844,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G775" t="n">
-        <v>1.22339844703674</v>
+        <v>1.22339832782745</v>
       </c>
       <c r="H775" t="n">
         <v>0</v>
@@ -22873,7 +22873,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G776" t="n">
-        <v>1.25666296482086</v>
+        <v>1.25666308403015</v>
       </c>
       <c r="H776" t="n">
         <v>21859</v>
@@ -22902,7 +22902,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G777" t="n">
-        <v>1.25666296482086</v>
+        <v>1.25666308403015</v>
       </c>
       <c r="H777" t="n">
         <v>12547</v>
@@ -22931,7 +22931,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G778" t="n">
-        <v>1.25666296482086</v>
+        <v>1.25666308403015</v>
       </c>
       <c r="H778" t="n">
         <v>101000</v>
@@ -23047,7 +23047,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G782" t="n">
-        <v>1.24557495117188</v>
+        <v>1.24557483196259</v>
       </c>
       <c r="H782" t="n">
         <v>3012</v>
@@ -23076,7 +23076,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G783" t="n">
-        <v>1.27144742012024</v>
+        <v>1.27144730091095</v>
       </c>
       <c r="H783" t="n">
         <v>18810</v>
@@ -23163,7 +23163,7 @@
         <v>1.75</v>
       </c>
       <c r="G786" t="n">
-        <v>1.29362368583679</v>
+        <v>1.29362380504608</v>
       </c>
       <c r="H786" t="n">
         <v>23218</v>
@@ -23192,7 +23192,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G787" t="n">
-        <v>1.28992772102356</v>
+        <v>1.28992760181427</v>
       </c>
       <c r="H787" t="n">
         <v>13365</v>
@@ -23250,7 +23250,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G789" t="n">
-        <v>1.31949627399445</v>
+        <v>1.31949615478516</v>
       </c>
       <c r="H789" t="n">
         <v>40069</v>
@@ -23337,7 +23337,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G792" t="n">
-        <v>1.25666296482086</v>
+        <v>1.25666308403015</v>
       </c>
       <c r="H792" t="n">
         <v>3032</v>
@@ -23424,7 +23424,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G795" t="n">
-        <v>1.27144742012024</v>
+        <v>1.27144730091095</v>
       </c>
       <c r="H795" t="n">
         <v>705</v>
@@ -23453,7 +23453,7 @@
         <v>1.75</v>
       </c>
       <c r="G796" t="n">
-        <v>1.29362368583679</v>
+        <v>1.29362380504608</v>
       </c>
       <c r="H796" t="n">
         <v>7363</v>
@@ -23656,7 +23656,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G803" t="n">
-        <v>1.35276079177856</v>
+        <v>1.35276091098785</v>
       </c>
       <c r="H803" t="n">
         <v>542</v>
@@ -23685,7 +23685,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G804" t="n">
-        <v>1.35276079177856</v>
+        <v>1.35276091098785</v>
       </c>
       <c r="H804" t="n">
         <v>8594</v>
@@ -23714,7 +23714,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G805" t="n">
-        <v>1.35276079177856</v>
+        <v>1.35276091098785</v>
       </c>
       <c r="H805" t="n">
         <v>2732</v>
@@ -23743,7 +23743,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G806" t="n">
-        <v>1.35276079177856</v>
+        <v>1.35276091098785</v>
       </c>
       <c r="H806" t="n">
         <v>1000</v>
@@ -23772,7 +23772,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G807" t="n">
-        <v>1.35276079177856</v>
+        <v>1.35276091098785</v>
       </c>
       <c r="H807" t="n">
         <v>0</v>
@@ -23801,7 +23801,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G808" t="n">
-        <v>1.35276079177856</v>
+        <v>1.35276091098785</v>
       </c>
       <c r="H808" t="n">
         <v>0</v>
@@ -23830,7 +23830,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G809" t="n">
-        <v>1.35276079177856</v>
+        <v>1.35276091098785</v>
       </c>
       <c r="H809" t="n">
         <v>5500</v>
@@ -23859,7 +23859,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G810" t="n">
-        <v>1.31949627399445</v>
+        <v>1.31949615478516</v>
       </c>
       <c r="H810" t="n">
         <v>2179</v>
@@ -24700,7 +24700,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G839" t="n">
-        <v>1.29731976985931</v>
+        <v>1.29731965065002</v>
       </c>
       <c r="H839" t="n">
         <v>4100</v>
@@ -24729,7 +24729,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G840" t="n">
-        <v>1.29731976985931</v>
+        <v>1.29731965065002</v>
       </c>
       <c r="H840" t="n">
         <v>0</v>
@@ -24758,7 +24758,7 @@
         <v>1.75</v>
       </c>
       <c r="G841" t="n">
-        <v>1.29362368583679</v>
+        <v>1.29362380504608</v>
       </c>
       <c r="H841" t="n">
         <v>946</v>
@@ -24787,7 +24787,7 @@
         <v>1.75</v>
       </c>
       <c r="G842" t="n">
-        <v>1.29362368583679</v>
+        <v>1.29362380504608</v>
       </c>
       <c r="H842" t="n">
         <v>1000</v>
@@ -24903,7 +24903,7 @@
         <v>1.75</v>
       </c>
       <c r="G846" t="n">
-        <v>1.29362368583679</v>
+        <v>1.29362380504608</v>
       </c>
       <c r="H846" t="n">
         <v>4138</v>
@@ -25222,7 +25222,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G857" t="n">
-        <v>1.25666296482086</v>
+        <v>1.25666308403015</v>
       </c>
       <c r="H857" t="n">
         <v>13958</v>
@@ -25251,7 +25251,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G858" t="n">
-        <v>1.27514326572418</v>
+        <v>1.27514338493347</v>
       </c>
       <c r="H858" t="n">
         <v>4429</v>
@@ -26005,7 +26005,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G884" t="n">
-        <v>1.32703864574432</v>
+        <v>1.32703876495361</v>
       </c>
       <c r="H884" t="n">
         <v>15683</v>
@@ -26092,7 +26092,7 @@
         <v>1.66499996185303</v>
       </c>
       <c r="G887" t="n">
-        <v>1.28088080883026</v>
+        <v>1.28088068962097</v>
       </c>
       <c r="H887" t="n">
         <v>16749</v>
@@ -26150,7 +26150,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G889" t="n">
-        <v>1.296266913414</v>
+        <v>1.29626679420471</v>
       </c>
       <c r="H889" t="n">
         <v>2947</v>
@@ -26237,7 +26237,7 @@
         <v>1.75</v>
       </c>
       <c r="G892" t="n">
-        <v>1.34627115726471</v>
+        <v>1.346271276474</v>
       </c>
       <c r="H892" t="n">
         <v>10919</v>
@@ -26295,7 +26295,7 @@
         <v>1.75</v>
       </c>
       <c r="G894" t="n">
-        <v>1.34627115726471</v>
+        <v>1.346271276474</v>
       </c>
       <c r="H894" t="n">
         <v>12138</v>
@@ -26324,7 +26324,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G895" t="n">
-        <v>1.35011768341064</v>
+        <v>1.35011756420135</v>
       </c>
       <c r="H895" t="n">
         <v>7847</v>
@@ -26353,7 +26353,7 @@
         <v>1.75</v>
       </c>
       <c r="G896" t="n">
-        <v>1.34627115726471</v>
+        <v>1.346271276474</v>
       </c>
       <c r="H896" t="n">
         <v>2773</v>
@@ -26817,7 +26817,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G912" t="n">
-        <v>1.44628000259399</v>
+        <v>1.4462798833847</v>
       </c>
       <c r="H912" t="n">
         <v>9083</v>
@@ -27078,7 +27078,7 @@
         <v>1.75</v>
       </c>
       <c r="G921" t="n">
-        <v>1.34627115726471</v>
+        <v>1.346271276474</v>
       </c>
       <c r="H921" t="n">
         <v>5892</v>
@@ -27136,7 +27136,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G923" t="n">
-        <v>1.37319672107697</v>
+        <v>1.37319660186768</v>
       </c>
       <c r="H923" t="n">
         <v>1212</v>
@@ -27368,7 +27368,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G931" t="n">
-        <v>1.35011768341064</v>
+        <v>1.35011756420135</v>
       </c>
       <c r="H931" t="n">
         <v>1966</v>
@@ -27542,7 +27542,7 @@
         <v>1.75</v>
       </c>
       <c r="G937" t="n">
-        <v>1.34627115726471</v>
+        <v>1.346271276474</v>
       </c>
       <c r="H937" t="n">
         <v>13257</v>
@@ -27571,7 +27571,7 @@
         <v>1.75</v>
       </c>
       <c r="G938" t="n">
-        <v>1.34627115726471</v>
+        <v>1.346271276474</v>
       </c>
       <c r="H938" t="n">
         <v>35955</v>
@@ -27600,7 +27600,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G939" t="n">
-        <v>1.34242475032806</v>
+        <v>1.34242463111877</v>
       </c>
       <c r="H939" t="n">
         <v>27702</v>
@@ -27629,7 +27629,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G940" t="n">
-        <v>1.34242475032806</v>
+        <v>1.34242463111877</v>
       </c>
       <c r="H940" t="n">
         <v>20009</v>
@@ -27658,7 +27658,7 @@
         <v>1.75</v>
       </c>
       <c r="G941" t="n">
-        <v>1.34627115726471</v>
+        <v>1.346271276474</v>
       </c>
       <c r="H941" t="n">
         <v>17230</v>
@@ -27716,7 +27716,7 @@
         <v>1.75</v>
       </c>
       <c r="G943" t="n">
-        <v>1.34627115726471</v>
+        <v>1.346271276474</v>
       </c>
       <c r="H943" t="n">
         <v>9000</v>
@@ -27745,7 +27745,7 @@
         <v>1.75</v>
       </c>
       <c r="G944" t="n">
-        <v>1.34627115726471</v>
+        <v>1.346271276474</v>
       </c>
       <c r="H944" t="n">
         <v>5763</v>
@@ -27803,7 +27803,7 @@
         <v>1.75</v>
       </c>
       <c r="G946" t="n">
-        <v>1.34627115726471</v>
+        <v>1.346271276474</v>
       </c>
       <c r="H946" t="n">
         <v>42552</v>
@@ -27832,7 +27832,7 @@
         <v>1.75</v>
       </c>
       <c r="G947" t="n">
-        <v>1.34627115726471</v>
+        <v>1.346271276474</v>
       </c>
       <c r="H947" t="n">
         <v>13059</v>
@@ -27890,7 +27890,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G949" t="n">
-        <v>1.32319235801697</v>
+        <v>1.32319223880768</v>
       </c>
       <c r="H949" t="n">
         <v>34402</v>
@@ -27948,7 +27948,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G951" t="n">
-        <v>1.34242475032806</v>
+        <v>1.34242463111877</v>
       </c>
       <c r="H951" t="n">
         <v>35679</v>
@@ -28006,7 +28006,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G953" t="n">
-        <v>1.32319235801697</v>
+        <v>1.32319223880768</v>
       </c>
       <c r="H953" t="n">
         <v>9908</v>
@@ -28093,7 +28093,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G956" t="n">
-        <v>1.30780625343323</v>
+        <v>1.30780637264252</v>
       </c>
       <c r="H956" t="n">
         <v>1059</v>
@@ -28180,7 +28180,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G959" t="n">
-        <v>1.32319235801697</v>
+        <v>1.32319223880768</v>
       </c>
       <c r="H959" t="n">
         <v>5006</v>
@@ -28209,7 +28209,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G960" t="n">
-        <v>1.32319235801697</v>
+        <v>1.32319223880768</v>
       </c>
       <c r="H960" t="n">
         <v>6606</v>
@@ -28325,7 +28325,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G964" t="n">
-        <v>1.32319235801697</v>
+        <v>1.32319223880768</v>
       </c>
       <c r="H964" t="n">
         <v>21299</v>
@@ -28354,7 +28354,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G965" t="n">
-        <v>1.32319235801697</v>
+        <v>1.32319223880768</v>
       </c>
       <c r="H965" t="n">
         <v>43147</v>
@@ -28383,7 +28383,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G966" t="n">
-        <v>1.32319235801697</v>
+        <v>1.32319223880768</v>
       </c>
       <c r="H966" t="n">
         <v>26244</v>
@@ -28412,7 +28412,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G967" t="n">
-        <v>1.32319235801697</v>
+        <v>1.32319223880768</v>
       </c>
       <c r="H967" t="n">
         <v>5709</v>
@@ -28499,7 +28499,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G970" t="n">
-        <v>1.32319235801697</v>
+        <v>1.32319223880768</v>
       </c>
       <c r="H970" t="n">
         <v>12770</v>
@@ -28528,7 +28528,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G971" t="n">
-        <v>1.32319235801697</v>
+        <v>1.32319223880768</v>
       </c>
       <c r="H971" t="n">
         <v>31361</v>
@@ -28557,7 +28557,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G972" t="n">
-        <v>1.32319235801697</v>
+        <v>1.32319223880768</v>
       </c>
       <c r="H972" t="n">
         <v>0</v>
@@ -28615,7 +28615,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G974" t="n">
-        <v>1.30780625343323</v>
+        <v>1.30780637264252</v>
       </c>
       <c r="H974" t="n">
         <v>10376</v>
@@ -28673,7 +28673,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G976" t="n">
-        <v>1.32319235801697</v>
+        <v>1.32319223880768</v>
       </c>
       <c r="H976" t="n">
         <v>17427</v>
@@ -28702,7 +28702,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G977" t="n">
-        <v>1.32319235801697</v>
+        <v>1.32319223880768</v>
       </c>
       <c r="H977" t="n">
         <v>11856</v>
@@ -28731,7 +28731,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G978" t="n">
-        <v>1.32319235801697</v>
+        <v>1.32319223880768</v>
       </c>
       <c r="H978" t="n">
         <v>13561</v>
@@ -28847,7 +28847,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G982" t="n">
-        <v>1.32319235801697</v>
+        <v>1.32319223880768</v>
       </c>
       <c r="H982" t="n">
         <v>10299</v>
@@ -28934,7 +28934,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G985" t="n">
-        <v>1.32703864574432</v>
+        <v>1.32703876495361</v>
       </c>
       <c r="H985" t="n">
         <v>72587</v>
@@ -28963,7 +28963,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G986" t="n">
-        <v>1.30780625343323</v>
+        <v>1.30780637264252</v>
       </c>
       <c r="H986" t="n">
         <v>17368</v>
@@ -28992,7 +28992,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G987" t="n">
-        <v>1.30011320114136</v>
+        <v>1.30011332035065</v>
       </c>
       <c r="H987" t="n">
         <v>24670</v>
@@ -29166,7 +29166,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G993" t="n">
-        <v>1.30780625343323</v>
+        <v>1.30780637264252</v>
       </c>
       <c r="H993" t="n">
         <v>38419</v>
@@ -29224,7 +29224,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G995" t="n">
-        <v>1.43089389801025</v>
+        <v>1.43089401721954</v>
       </c>
       <c r="H995" t="n">
         <v>134459</v>
@@ -29253,7 +29253,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G996" t="n">
-        <v>1.42320096492767</v>
+        <v>1.42320108413696</v>
       </c>
       <c r="H996" t="n">
         <v>63062</v>
@@ -29311,7 +29311,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G998" t="n">
-        <v>1.43089389801025</v>
+        <v>1.43089401721954</v>
       </c>
       <c r="H998" t="n">
         <v>43327</v>
@@ -29340,7 +29340,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G999" t="n">
-        <v>1.40781497955322</v>
+        <v>1.40781509876251</v>
       </c>
       <c r="H999" t="n">
         <v>19336</v>
@@ -29398,7 +29398,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1001" t="n">
-        <v>1.40781497955322</v>
+        <v>1.40781509876251</v>
       </c>
       <c r="H1001" t="n">
         <v>21345</v>
@@ -29456,7 +29456,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1003" t="n">
-        <v>1.42320096492767</v>
+        <v>1.42320108413696</v>
       </c>
       <c r="H1003" t="n">
         <v>6433</v>
@@ -29543,7 +29543,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1006" t="n">
-        <v>1.42320096492767</v>
+        <v>1.42320108413696</v>
       </c>
       <c r="H1006" t="n">
         <v>11431</v>
@@ -29572,7 +29572,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1007" t="n">
-        <v>1.42320096492767</v>
+        <v>1.42320108413696</v>
       </c>
       <c r="H1007" t="n">
         <v>4487</v>
@@ -29659,7 +29659,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1010" t="n">
-        <v>1.46166574954987</v>
+        <v>1.46166586875916</v>
       </c>
       <c r="H1010" t="n">
         <v>4227</v>
@@ -29688,7 +29688,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1011" t="n">
-        <v>1.46166574954987</v>
+        <v>1.46166586875916</v>
       </c>
       <c r="H1011" t="n">
         <v>1754</v>
@@ -29717,7 +29717,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1012" t="n">
-        <v>1.46166574954987</v>
+        <v>1.46166586875916</v>
       </c>
       <c r="H1012" t="n">
         <v>18675</v>
@@ -29833,7 +29833,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1016" t="n">
-        <v>1.50782370567322</v>
+        <v>1.50782382488251</v>
       </c>
       <c r="H1016" t="n">
         <v>7232</v>
@@ -29920,7 +29920,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1019" t="n">
-        <v>1.44628000259399</v>
+        <v>1.4462798833847</v>
       </c>
       <c r="H1019" t="n">
         <v>6583</v>
@@ -29949,7 +29949,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1020" t="n">
-        <v>1.44628000259399</v>
+        <v>1.4462798833847</v>
       </c>
       <c r="H1020" t="n">
         <v>1006</v>
@@ -30036,7 +30036,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1023" t="n">
-        <v>1.53090262413025</v>
+        <v>1.53090274333954</v>
       </c>
       <c r="H1023" t="n">
         <v>45318</v>
@@ -30065,7 +30065,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1024" t="n">
-        <v>1.50013077259064</v>
+        <v>1.50013089179993</v>
       </c>
       <c r="H1024" t="n">
         <v>16891</v>
@@ -30094,7 +30094,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1025" t="n">
-        <v>1.49243783950806</v>
+        <v>1.49243795871735</v>
       </c>
       <c r="H1025" t="n">
         <v>26509</v>
@@ -30123,7 +30123,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1026" t="n">
-        <v>1.49243783950806</v>
+        <v>1.49243795871735</v>
       </c>
       <c r="H1026" t="n">
         <v>3629</v>
@@ -30152,7 +30152,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1027" t="n">
-        <v>1.50013077259064</v>
+        <v>1.50013089179993</v>
       </c>
       <c r="H1027" t="n">
         <v>12968</v>
@@ -30239,7 +30239,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1030" t="n">
-        <v>1.46166574954987</v>
+        <v>1.46166586875916</v>
       </c>
       <c r="H1030" t="n">
         <v>3337</v>
@@ -30268,7 +30268,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1031" t="n">
-        <v>1.46166574954987</v>
+        <v>1.46166586875916</v>
       </c>
       <c r="H1031" t="n">
         <v>38168</v>
@@ -30297,7 +30297,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1032" t="n">
-        <v>1.46166574954987</v>
+        <v>1.46166586875916</v>
       </c>
       <c r="H1032" t="n">
         <v>7715</v>
@@ -30384,7 +30384,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.48859119415283</v>
+        <v>1.48859131336212</v>
       </c>
       <c r="H1035" t="n">
         <v>21886</v>
@@ -30413,7 +30413,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G1036" t="n">
-        <v>1.49628436565399</v>
+        <v>1.4962842464447</v>
       </c>
       <c r="H1036" t="n">
         <v>4366</v>
@@ -30442,7 +30442,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1037" t="n">
-        <v>1.46935880184174</v>
+        <v>1.46935892105103</v>
       </c>
       <c r="H1037" t="n">
         <v>5007</v>
@@ -30558,7 +30558,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1041" t="n">
-        <v>1.61552536487579</v>
+        <v>1.61552548408508</v>
       </c>
       <c r="H1041" t="n">
         <v>69685</v>
@@ -30674,7 +30674,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1045" t="n">
-        <v>2.07710409164429</v>
+        <v>2.07710433006287</v>
       </c>
       <c r="H1045" t="n">
         <v>256117</v>
@@ -30761,7 +30761,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1048" t="n">
-        <v>2.07710409164429</v>
+        <v>2.07710433006287</v>
       </c>
       <c r="H1048" t="n">
         <v>133309</v>
@@ -30848,7 +30848,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1051" t="n">
-        <v>2.13864779472351</v>
+        <v>2.13864803314209</v>
       </c>
       <c r="H1051" t="n">
         <v>100657</v>
@@ -30877,7 +30877,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1052" t="n">
-        <v>2.14634108543396</v>
+        <v>2.14634084701538</v>
       </c>
       <c r="H1052" t="n">
         <v>84567</v>
@@ -30964,7 +30964,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1055" t="n">
-        <v>2.07710409164429</v>
+        <v>2.07710433006287</v>
       </c>
       <c r="H1055" t="n">
         <v>12892</v>
@@ -31080,7 +31080,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1059" t="n">
-        <v>1.76169204711914</v>
+        <v>1.76169180870056</v>
       </c>
       <c r="H1059" t="n">
         <v>11322</v>
@@ -31109,7 +31109,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1060" t="n">
-        <v>1.84631502628326</v>
+        <v>1.84631478786469</v>
       </c>
       <c r="H1060" t="n">
         <v>41804</v>
@@ -31196,7 +31196,7 @@
         <v>1.75</v>
       </c>
       <c r="G1063" t="n">
-        <v>1.34627115726471</v>
+        <v>1.346271276474</v>
       </c>
       <c r="H1063" t="n">
         <v>35343</v>
@@ -31254,7 +31254,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1065" t="n">
-        <v>1.46166574954987</v>
+        <v>1.46166586875916</v>
       </c>
       <c r="H1065" t="n">
         <v>15990</v>
@@ -31370,7 +31370,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1069" t="n">
-        <v>1.40781497955322</v>
+        <v>1.40781509876251</v>
       </c>
       <c r="H1069" t="n">
         <v>2084</v>
@@ -31399,7 +31399,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1070" t="n">
-        <v>1.42320096492767</v>
+        <v>1.42320108413696</v>
       </c>
       <c r="H1070" t="n">
         <v>3757</v>
@@ -31544,7 +31544,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1075" t="n">
-        <v>1.34242475032806</v>
+        <v>1.34242463111877</v>
       </c>
       <c r="H1075" t="n">
         <v>22077</v>
@@ -31573,7 +31573,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1076" t="n">
-        <v>1.30780625343323</v>
+        <v>1.30780637264252</v>
       </c>
       <c r="H1076" t="n">
         <v>20427</v>
@@ -31602,7 +31602,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1077" t="n">
-        <v>1.30780625343323</v>
+        <v>1.30780637264252</v>
       </c>
       <c r="H1077" t="n">
         <v>2916</v>
@@ -31631,7 +31631,7 @@
         <v>1.75</v>
       </c>
       <c r="G1078" t="n">
-        <v>1.34627115726471</v>
+        <v>1.346271276474</v>
       </c>
       <c r="H1078" t="n">
         <v>5091</v>
@@ -31689,7 +31689,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1080" t="n">
-        <v>1.37319672107697</v>
+        <v>1.37319660186768</v>
       </c>
       <c r="H1080" t="n">
         <v>38293</v>
@@ -31718,7 +31718,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1081" t="n">
-        <v>1.43089389801025</v>
+        <v>1.43089401721954</v>
       </c>
       <c r="H1081" t="n">
         <v>18831</v>
@@ -31747,7 +31747,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1082" t="n">
-        <v>1.46166574954987</v>
+        <v>1.46166586875916</v>
       </c>
       <c r="H1082" t="n">
         <v>12007</v>
@@ -31805,7 +31805,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1084" t="n">
-        <v>1.66168320178986</v>
+        <v>1.66168332099915</v>
       </c>
       <c r="H1084" t="n">
         <v>34019</v>
@@ -31921,7 +31921,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1088" t="n">
-        <v>1.58475339412689</v>
+        <v>1.58475351333618</v>
       </c>
       <c r="H1088" t="n">
         <v>28484</v>
@@ -31950,7 +31950,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1089" t="n">
-        <v>1.62321829795837</v>
+        <v>1.62321841716766</v>
       </c>
       <c r="H1089" t="n">
         <v>4439</v>
@@ -31979,7 +31979,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1090" t="n">
-        <v>1.62321829795837</v>
+        <v>1.62321841716766</v>
       </c>
       <c r="H1090" t="n">
         <v>1196</v>
@@ -32008,7 +32008,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1091" t="n">
-        <v>1.58475339412689</v>
+        <v>1.58475351333618</v>
       </c>
       <c r="H1091" t="n">
         <v>1313</v>
@@ -32037,7 +32037,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1092" t="n">
-        <v>1.5462886095047</v>
+        <v>1.54628872871399</v>
       </c>
       <c r="H1092" t="n">
         <v>16140</v>
@@ -32211,7 +32211,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1098" t="n">
-        <v>1.65399038791656</v>
+        <v>1.65399050712585</v>
       </c>
       <c r="H1098" t="n">
         <v>6470</v>
@@ -32240,7 +32240,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1099" t="n">
-        <v>1.65399038791656</v>
+        <v>1.65399050712585</v>
       </c>
       <c r="H1099" t="n">
         <v>7967</v>
@@ -32269,7 +32269,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1100" t="n">
-        <v>1.65399038791656</v>
+        <v>1.65399050712585</v>
       </c>
       <c r="H1100" t="n">
         <v>0</v>
@@ -32298,7 +32298,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1101" t="n">
-        <v>1.62321829795837</v>
+        <v>1.62321841716766</v>
       </c>
       <c r="H1101" t="n">
         <v>3168</v>
@@ -32327,7 +32327,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1102" t="n">
-        <v>1.61552536487579</v>
+        <v>1.61552548408508</v>
       </c>
       <c r="H1102" t="n">
         <v>5156</v>
@@ -32356,7 +32356,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1103" t="n">
-        <v>1.58475339412689</v>
+        <v>1.58475351333618</v>
       </c>
       <c r="H1103" t="n">
         <v>2176</v>
@@ -32414,7 +32414,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1105" t="n">
-        <v>1.56167459487915</v>
+        <v>1.56167471408844</v>
       </c>
       <c r="H1105" t="n">
         <v>1638</v>
@@ -32530,7 +32530,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1109" t="n">
-        <v>1.5462886095047</v>
+        <v>1.54628872871399</v>
       </c>
       <c r="H1109" t="n">
         <v>1802</v>
@@ -32646,7 +32646,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1113" t="n">
-        <v>1.56167459487915</v>
+        <v>1.56167471408844</v>
       </c>
       <c r="H1113" t="n">
         <v>1000</v>
@@ -32733,7 +32733,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1116" t="n">
-        <v>1.5462886095047</v>
+        <v>1.54628872871399</v>
       </c>
       <c r="H1116" t="n">
         <v>6736</v>
@@ -32820,7 +32820,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1119" t="n">
-        <v>1.56167459487915</v>
+        <v>1.56167471408844</v>
       </c>
       <c r="H1119" t="n">
         <v>7191</v>
@@ -32965,7 +32965,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1124" t="n">
-        <v>1.61552536487579</v>
+        <v>1.61552548408508</v>
       </c>
       <c r="H1124" t="n">
         <v>2966</v>
@@ -33023,7 +33023,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1126" t="n">
-        <v>1.65399038791656</v>
+        <v>1.65399050712585</v>
       </c>
       <c r="H1126" t="n">
         <v>4853</v>
@@ -33081,7 +33081,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1128" t="n">
-        <v>1.66168320178986</v>
+        <v>1.66168332099915</v>
       </c>
       <c r="H1128" t="n">
         <v>6116</v>
@@ -33168,7 +33168,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1131" t="n">
-        <v>1.88477969169617</v>
+        <v>1.88477957248688</v>
       </c>
       <c r="H1131" t="n">
         <v>47259</v>
@@ -33197,7 +33197,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1132" t="n">
-        <v>1.88477969169617</v>
+        <v>1.88477957248688</v>
       </c>
       <c r="H1132" t="n">
         <v>29383</v>
@@ -33255,7 +33255,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1134" t="n">
-        <v>1.88477969169617</v>
+        <v>1.88477957248688</v>
       </c>
       <c r="H1134" t="n">
         <v>18941</v>
@@ -33284,7 +33284,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1135" t="n">
-        <v>1.87682712078094</v>
+        <v>1.87682688236237</v>
       </c>
       <c r="H1135" t="n">
         <v>18831</v>
@@ -33342,7 +33342,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1137" t="n">
-        <v>1.83706367015839</v>
+        <v>1.8370635509491</v>
       </c>
       <c r="H1137" t="n">
         <v>7476</v>
@@ -33371,7 +33371,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1138" t="n">
-        <v>1.83706367015839</v>
+        <v>1.8370635509491</v>
       </c>
       <c r="H1138" t="n">
         <v>9410</v>
@@ -33400,7 +33400,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1139" t="n">
-        <v>1.83706367015839</v>
+        <v>1.8370635509491</v>
       </c>
       <c r="H1139" t="n">
         <v>2123</v>
@@ -33429,7 +33429,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1140" t="n">
-        <v>1.83706367015839</v>
+        <v>1.8370635509491</v>
       </c>
       <c r="H1140" t="n">
         <v>1401</v>
@@ -33661,7 +33661,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1148" t="n">
-        <v>1.69391596317291</v>
+        <v>1.6939160823822</v>
       </c>
       <c r="H1148" t="n">
         <v>3447</v>
@@ -33719,7 +33719,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1150" t="n">
-        <v>1.7336790561676</v>
+        <v>1.73367929458618</v>
       </c>
       <c r="H1150" t="n">
         <v>5394</v>
@@ -33806,7 +33806,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1153" t="n">
-        <v>1.6780104637146</v>
+        <v>1.67801058292389</v>
       </c>
       <c r="H1153" t="n">
         <v>400</v>
@@ -33835,7 +33835,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1154" t="n">
-        <v>1.71777391433716</v>
+        <v>1.71777403354645</v>
       </c>
       <c r="H1154" t="n">
         <v>8433</v>
@@ -33864,7 +33864,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1155" t="n">
-        <v>1.71777391433716</v>
+        <v>1.71777403354645</v>
       </c>
       <c r="H1155" t="n">
         <v>0</v>
@@ -33951,7 +33951,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1158" t="n">
-        <v>1.69391596317291</v>
+        <v>1.6939160823822</v>
       </c>
       <c r="H1158" t="n">
         <v>500</v>
@@ -33980,7 +33980,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1159" t="n">
-        <v>1.6700576543808</v>
+        <v>1.67005777359009</v>
       </c>
       <c r="H1159" t="n">
         <v>5589</v>
@@ -34067,7 +34067,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1162" t="n">
-        <v>1.6780104637146</v>
+        <v>1.67801058292389</v>
       </c>
       <c r="H1162" t="n">
         <v>5772</v>
@@ -34096,7 +34096,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1163" t="n">
-        <v>1.68596303462982</v>
+        <v>1.68596315383911</v>
       </c>
       <c r="H1163" t="n">
         <v>3283</v>
@@ -34125,7 +34125,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1164" t="n">
-        <v>1.68596303462982</v>
+        <v>1.68596315383911</v>
       </c>
       <c r="H1164" t="n">
         <v>0</v>
@@ -34154,7 +34154,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1165" t="n">
-        <v>1.68596303462982</v>
+        <v>1.68596315383911</v>
       </c>
       <c r="H1165" t="n">
         <v>350</v>
@@ -34183,7 +34183,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1166" t="n">
-        <v>1.6780104637146</v>
+        <v>1.67801058292389</v>
       </c>
       <c r="H1166" t="n">
         <v>500</v>
@@ -34270,7 +34270,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1169" t="n">
-        <v>1.6700576543808</v>
+        <v>1.67005777359009</v>
       </c>
       <c r="H1169" t="n">
         <v>166</v>
@@ -34299,7 +34299,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1170" t="n">
-        <v>1.6700576543808</v>
+        <v>1.67005777359009</v>
       </c>
       <c r="H1170" t="n">
         <v>646</v>
@@ -34328,7 +34328,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1171" t="n">
-        <v>1.68596303462982</v>
+        <v>1.68596315383911</v>
       </c>
       <c r="H1171" t="n">
         <v>875</v>
@@ -34415,7 +34415,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1174" t="n">
-        <v>1.62234175205231</v>
+        <v>1.6223418712616</v>
       </c>
       <c r="H1174" t="n">
         <v>3550</v>
@@ -34502,7 +34502,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1177" t="n">
-        <v>1.61438930034637</v>
+        <v>1.61438941955566</v>
       </c>
       <c r="H1177" t="n">
         <v>1235</v>
@@ -34531,7 +34531,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1178" t="n">
-        <v>1.60643661022186</v>
+        <v>1.60643672943115</v>
       </c>
       <c r="H1178" t="n">
         <v>600</v>
@@ -34560,7 +34560,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1179" t="n">
-        <v>1.59848392009735</v>
+        <v>1.59848403930664</v>
       </c>
       <c r="H1179" t="n">
         <v>1525</v>
@@ -34734,7 +34734,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1185" t="n">
-        <v>1.69391596317291</v>
+        <v>1.6939160823822</v>
       </c>
       <c r="H1185" t="n">
         <v>610</v>
@@ -34763,7 +34763,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1186" t="n">
-        <v>1.61438930034637</v>
+        <v>1.61438941955566</v>
       </c>
       <c r="H1186" t="n">
         <v>4490</v>
@@ -34792,7 +34792,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1187" t="n">
-        <v>1.61438930034637</v>
+        <v>1.61438941955566</v>
       </c>
       <c r="H1187" t="n">
         <v>4693</v>
@@ -34850,7 +34850,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1189" t="n">
-        <v>1.59848392009735</v>
+        <v>1.59848403930664</v>
       </c>
       <c r="H1189" t="n">
         <v>1023</v>
@@ -34879,7 +34879,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1190" t="n">
-        <v>1.60643661022186</v>
+        <v>1.60643672943115</v>
       </c>
       <c r="H1190" t="n">
         <v>3027</v>
@@ -35140,7 +35140,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1199" t="n">
-        <v>1.61438930034637</v>
+        <v>1.61438941955566</v>
       </c>
       <c r="H1199" t="n">
         <v>1561</v>
@@ -35169,7 +35169,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1200" t="n">
-        <v>1.59848392009735</v>
+        <v>1.59848403930664</v>
       </c>
       <c r="H1200" t="n">
         <v>1014</v>
@@ -35198,7 +35198,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1201" t="n">
-        <v>1.61438930034637</v>
+        <v>1.61438941955566</v>
       </c>
       <c r="H1201" t="n">
         <v>5684</v>
@@ -35256,7 +35256,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1203" t="n">
-        <v>1.62234175205231</v>
+        <v>1.6223418712616</v>
       </c>
       <c r="H1203" t="n">
         <v>4216</v>
@@ -35285,7 +35285,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1204" t="n">
-        <v>1.62234175205231</v>
+        <v>1.6223418712616</v>
       </c>
       <c r="H1204" t="n">
         <v>500</v>
@@ -35488,7 +35488,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1211" t="n">
-        <v>1.62234175205231</v>
+        <v>1.6223418712616</v>
       </c>
       <c r="H1211" t="n">
         <v>1549</v>
@@ -35575,7 +35575,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1214" t="n">
-        <v>1.62234175205231</v>
+        <v>1.6223418712616</v>
       </c>
       <c r="H1214" t="n">
         <v>1017</v>
@@ -35633,7 +35633,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1216" t="n">
-        <v>1.60643661022186</v>
+        <v>1.60643672943115</v>
       </c>
       <c r="H1216" t="n">
         <v>210</v>
@@ -35691,7 +35691,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1218" t="n">
-        <v>1.60643661022186</v>
+        <v>1.60643672943115</v>
       </c>
       <c r="H1218" t="n">
         <v>3357</v>
@@ -35720,7 +35720,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1219" t="n">
-        <v>1.60643661022186</v>
+        <v>1.60643672943115</v>
       </c>
       <c r="H1219" t="n">
         <v>0</v>
@@ -35952,7 +35952,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1227" t="n">
-        <v>1.55076801776886</v>
+        <v>1.55076813697815</v>
       </c>
       <c r="H1227" t="n">
         <v>3092</v>
@@ -36126,7 +36126,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1233" t="n">
-        <v>1.62234175205231</v>
+        <v>1.6223418712616</v>
       </c>
       <c r="H1233" t="n">
         <v>6224</v>
@@ -36155,7 +36155,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1234" t="n">
-        <v>1.62234175205231</v>
+        <v>1.6223418712616</v>
       </c>
       <c r="H1234" t="n">
         <v>0</v>
@@ -36242,7 +36242,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1237" t="n">
-        <v>1.60643661022186</v>
+        <v>1.60643672943115</v>
       </c>
       <c r="H1237" t="n">
         <v>786</v>
@@ -36271,7 +36271,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1238" t="n">
-        <v>1.60643661022186</v>
+        <v>1.60643672943115</v>
       </c>
       <c r="H1238" t="n">
         <v>405</v>
@@ -36300,7 +36300,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1239" t="n">
-        <v>1.62234175205231</v>
+        <v>1.6223418712616</v>
       </c>
       <c r="H1239" t="n">
         <v>6952</v>
@@ -36561,7 +36561,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1248" t="n">
-        <v>1.6700576543808</v>
+        <v>1.67005777359009</v>
       </c>
       <c r="H1248" t="n">
         <v>480</v>
@@ -36590,7 +36590,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1249" t="n">
-        <v>1.6700576543808</v>
+        <v>1.67005777359009</v>
       </c>
       <c r="H1249" t="n">
         <v>3277</v>
@@ -36648,7 +36648,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1251" t="n">
-        <v>1.7336790561676</v>
+        <v>1.73367929458618</v>
       </c>
       <c r="H1251" t="n">
         <v>14775</v>
@@ -36706,7 +36706,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1253" t="n">
-        <v>1.88477957248688</v>
+        <v>1.88477945327759</v>
       </c>
       <c r="H1253" t="n">
         <v>56170</v>
@@ -36764,7 +36764,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1255" t="n">
-        <v>1.87682712078094</v>
+        <v>1.87682688236237</v>
       </c>
       <c r="H1255" t="n">
         <v>4581</v>
@@ -36822,7 +36822,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1257" t="n">
-        <v>1.86887419223785</v>
+        <v>1.86887395381927</v>
       </c>
       <c r="H1257" t="n">
         <v>4013</v>
@@ -36880,7 +36880,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1259" t="n">
-        <v>1.80525302886963</v>
+        <v>1.80525279045105</v>
       </c>
       <c r="H1259" t="n">
         <v>11152</v>
@@ -36996,7 +36996,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1263" t="n">
-        <v>1.82115852832794</v>
+        <v>1.82115828990936</v>
       </c>
       <c r="H1263" t="n">
         <v>1893</v>
@@ -37025,7 +37025,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1264" t="n">
-        <v>1.82115852832794</v>
+        <v>1.82115828990936</v>
       </c>
       <c r="H1264" t="n">
         <v>100</v>
@@ -37054,7 +37054,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1265" t="n">
-        <v>1.82115852832794</v>
+        <v>1.82115828990936</v>
       </c>
       <c r="H1265" t="n">
         <v>2265</v>
@@ -37112,7 +37112,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1267" t="n">
-        <v>1.80525302886963</v>
+        <v>1.80525279045105</v>
       </c>
       <c r="H1267" t="n">
         <v>1755</v>
@@ -37257,7 +37257,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1272" t="n">
-        <v>1.86887419223785</v>
+        <v>1.86887395381927</v>
       </c>
       <c r="H1272" t="n">
         <v>3254</v>
@@ -37286,7 +37286,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1273" t="n">
-        <v>1.85296893119812</v>
+        <v>1.85296881198883</v>
       </c>
       <c r="H1273" t="n">
         <v>1802</v>
@@ -37344,7 +37344,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1275" t="n">
-        <v>1.86887419223785</v>
+        <v>1.86887395381927</v>
       </c>
       <c r="H1275" t="n">
         <v>12008</v>
@@ -37373,7 +37373,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1276" t="n">
-        <v>1.83706367015839</v>
+        <v>1.8370635509491</v>
       </c>
       <c r="H1276" t="n">
         <v>8858</v>
@@ -37431,7 +37431,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1278" t="n">
-        <v>1.83706367015839</v>
+        <v>1.8370635509491</v>
       </c>
       <c r="H1278" t="n">
         <v>6162</v>
@@ -37460,7 +37460,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1279" t="n">
-        <v>1.83706367015839</v>
+        <v>1.8370635509491</v>
       </c>
       <c r="H1279" t="n">
         <v>0</v>
@@ -37518,7 +37518,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1281" t="n">
-        <v>1.87682712078094</v>
+        <v>1.87682688236237</v>
       </c>
       <c r="H1281" t="n">
         <v>4358</v>
@@ -37750,7 +37750,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1289" t="n">
-        <v>1.80525302886963</v>
+        <v>1.80525279045105</v>
       </c>
       <c r="H1289" t="n">
         <v>331</v>
@@ -37779,7 +37779,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1290" t="n">
-        <v>1.82115852832794</v>
+        <v>1.82115828990936</v>
       </c>
       <c r="H1290" t="n">
         <v>1496</v>
@@ -37866,7 +37866,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1293" t="n">
-        <v>1.82115852832794</v>
+        <v>1.82115828990936</v>
       </c>
       <c r="H1293" t="n">
         <v>505</v>
@@ -37924,7 +37924,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1295" t="n">
-        <v>1.82115852832794</v>
+        <v>1.82115828990936</v>
       </c>
       <c r="H1295" t="n">
         <v>7335</v>
@@ -37982,7 +37982,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1297" t="n">
-        <v>1.86887419223785</v>
+        <v>1.86887395381927</v>
       </c>
       <c r="H1297" t="n">
         <v>31</v>
@@ -38011,7 +38011,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1298" t="n">
-        <v>1.83706367015839</v>
+        <v>1.8370635509491</v>
       </c>
       <c r="H1298" t="n">
         <v>3271</v>
@@ -38040,7 +38040,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1299" t="n">
-        <v>1.85296893119812</v>
+        <v>1.85296881198883</v>
       </c>
       <c r="H1299" t="n">
         <v>582</v>
@@ -38069,7 +38069,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1300" t="n">
-        <v>1.86887419223785</v>
+        <v>1.86887395381927</v>
       </c>
       <c r="H1300" t="n">
         <v>7992</v>
@@ -38098,7 +38098,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1301" t="n">
-        <v>1.88477957248688</v>
+        <v>1.88477945327759</v>
       </c>
       <c r="H1301" t="n">
         <v>6086</v>
@@ -38214,7 +38214,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1305" t="n">
-        <v>1.86887419223785</v>
+        <v>1.86887395381927</v>
       </c>
       <c r="H1305" t="n">
         <v>1311</v>
@@ -38243,7 +38243,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1306" t="n">
-        <v>1.83706367015839</v>
+        <v>1.8370635509491</v>
       </c>
       <c r="H1306" t="n">
         <v>710</v>
@@ -38330,7 +38330,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1309" t="n">
-        <v>1.85296893119812</v>
+        <v>1.85296881198883</v>
       </c>
       <c r="H1309" t="n">
         <v>1136</v>
@@ -38388,7 +38388,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1311" t="n">
-        <v>1.83706367015839</v>
+        <v>1.8370635509491</v>
       </c>
       <c r="H1311" t="n">
         <v>538</v>
@@ -38533,7 +38533,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1316" t="n">
-        <v>1.82115852832794</v>
+        <v>1.82115828990936</v>
       </c>
       <c r="H1316" t="n">
         <v>628</v>
@@ -38620,7 +38620,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1319" t="n">
-        <v>1.82115852832794</v>
+        <v>1.82115828990936</v>
       </c>
       <c r="H1319" t="n">
         <v>3940</v>
@@ -38852,7 +38852,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1327" t="n">
-        <v>1.82115852832794</v>
+        <v>1.82115828990936</v>
       </c>
       <c r="H1327" t="n">
         <v>21101</v>
@@ -38910,7 +38910,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1329" t="n">
-        <v>1.80525302886963</v>
+        <v>1.80525279045105</v>
       </c>
       <c r="H1329" t="n">
         <v>21301</v>
@@ -38997,7 +38997,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1332" t="n">
-        <v>1.82115852832794</v>
+        <v>1.82115828990936</v>
       </c>
       <c r="H1332" t="n">
         <v>2958</v>
@@ -39026,7 +39026,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1333" t="n">
-        <v>1.85296893119812</v>
+        <v>1.85296881198883</v>
       </c>
       <c r="H1333" t="n">
         <v>6107</v>
@@ -39142,7 +39142,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1337" t="n">
-        <v>1.82115852832794</v>
+        <v>1.82115828990936</v>
       </c>
       <c r="H1337" t="n">
         <v>2235</v>
@@ -39171,7 +39171,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1338" t="n">
-        <v>1.85296893119812</v>
+        <v>1.85296881198883</v>
       </c>
       <c r="H1338" t="n">
         <v>3845</v>
@@ -39200,7 +39200,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1339" t="n">
-        <v>1.83706367015839</v>
+        <v>1.8370635509491</v>
       </c>
       <c r="H1339" t="n">
         <v>14311</v>
@@ -39229,7 +39229,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1340" t="n">
-        <v>1.83706367015839</v>
+        <v>1.8370635509491</v>
       </c>
       <c r="H1340" t="n">
         <v>0</v>
@@ -39258,7 +39258,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1341" t="n">
-        <v>1.83706367015839</v>
+        <v>1.8370635509491</v>
       </c>
       <c r="H1341" t="n">
         <v>2500</v>
@@ -39374,7 +39374,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1345" t="n">
-        <v>1.85296893119812</v>
+        <v>1.85296881198883</v>
       </c>
       <c r="H1345" t="n">
         <v>2859</v>
@@ -39461,7 +39461,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1348" t="n">
-        <v>1.82115852832794</v>
+        <v>1.82115828990936</v>
       </c>
       <c r="H1348" t="n">
         <v>16910</v>
@@ -39577,7 +39577,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1352" t="n">
-        <v>1.83706367015839</v>
+        <v>1.8370635509491</v>
       </c>
       <c r="H1352" t="n">
         <v>21285</v>
@@ -39606,7 +39606,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1353" t="n">
-        <v>1.88477957248688</v>
+        <v>1.88477945327759</v>
       </c>
       <c r="H1353" t="n">
         <v>6970</v>
@@ -39635,7 +39635,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1354" t="n">
-        <v>1.88477957248688</v>
+        <v>1.88477945327759</v>
       </c>
       <c r="H1354" t="n">
         <v>26822</v>
@@ -39664,7 +39664,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1355" t="n">
-        <v>1.88477957248688</v>
+        <v>1.88477945327759</v>
       </c>
       <c r="H1355" t="n">
         <v>20320</v>
@@ -39722,7 +39722,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1357" t="n">
-        <v>1.87682712078094</v>
+        <v>1.87682688236237</v>
       </c>
       <c r="H1357" t="n">
         <v>2945</v>
@@ -39867,7 +39867,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1362" t="n">
-        <v>1.88477957248688</v>
+        <v>1.88477945327759</v>
       </c>
       <c r="H1362" t="n">
         <v>10631</v>
@@ -39925,7 +39925,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1364" t="n">
-        <v>1.87682712078094</v>
+        <v>1.87682688236237</v>
       </c>
       <c r="H1364" t="n">
         <v>6780</v>
@@ -39983,7 +39983,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1366" t="n">
-        <v>1.88477957248688</v>
+        <v>1.88477945327759</v>
       </c>
       <c r="H1366" t="n">
         <v>5497</v>
@@ -40070,7 +40070,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1369" t="n">
-        <v>1.88477957248688</v>
+        <v>1.88477945327759</v>
       </c>
       <c r="H1369" t="n">
         <v>1333</v>
@@ -40099,7 +40099,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1370" t="n">
-        <v>1.88477957248688</v>
+        <v>1.88477945327759</v>
       </c>
       <c r="H1370" t="n">
         <v>475</v>
@@ -40360,7 +40360,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1379" t="n">
-        <v>2.09154868125916</v>
+        <v>2.09154844284058</v>
       </c>
       <c r="H1379" t="n">
         <v>12850</v>
@@ -40563,7 +40563,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1386" t="n">
-        <v>2.09154868125916</v>
+        <v>2.09154844284058</v>
       </c>
       <c r="H1386" t="n">
         <v>5110</v>
